--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="Rc1cd44ec50a249be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R621839dc00424df8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -120,7 +120,7 @@
       <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
-  <x:fills count="11">
+  <x:fills count="17">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -172,8 +172,38 @@
         <x:fgColor rgb="FFF5F8FB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF4472C4"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9E2F3"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="11">
+  <x:borders count="12">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -267,11 +297,25 @@
         <x:color rgb="FFD7E0E8"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB8C4D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="101">
+  <x:cellXfs count="115">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -675,6 +719,53 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="13" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="14" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="15" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="16" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -896,1497 +987,1876 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="8" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="27" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="8" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="8" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="29" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="8" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="8" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="8" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="12" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="12" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="12" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="30" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
-      <x:c r="A1" s="70" t="str">
+      <x:c r="A1" s="110" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B1" s="70" t="str">
+      <x:c r="B1" s="110" t="str">
         <x:v>full_name</x:v>
       </x:c>
-      <x:c r="C1" s="70" t="str">
+      <x:c r="C1" s="110" t="str">
         <x:v>flags</x:v>
       </x:c>
-      <x:c r="D1" s="70" t="str">
+      <x:c r="D1" s="110" t="str">
         <x:v>unique</x:v>
       </x:c>
-      <x:c r="E1" s="70" t="str">
+      <x:c r="E1" s="110" t="str">
         <x:v>group</x:v>
       </x:c>
-      <x:c r="F1" s="70" t="str">
+      <x:c r="F1" s="110" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="G1" s="70" t="str">
+      <x:c r="G1" s="110" t="str">
         <x:v>tags</x:v>
       </x:c>
-      <x:c r="H1" s="70" t="str">
+      <x:c r="H1" s="110" t="str">
         <x:v>*items</x:v>
       </x:c>
-      <x:c r="I1" s="70"/>
-      <x:c r="J1" s="70"/>
-      <x:c r="K1" s="70"/>
-      <x:c r="L1" s="70"/>
+      <x:c r="I1" s="110"/>
+      <x:c r="J1" s="110"/>
+      <x:c r="K1" s="110"/>
+      <x:c r="L1" s="110"/>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
-      <x:c r="A2" s="72" t="str">
+      <x:c r="A2" s="112" t="str">
         <x:v>##var</x:v>
       </x:c>
-      <x:c r="B2" s="72"/>
-      <x:c r="C2" s="72"/>
-      <x:c r="D2" s="72"/>
-      <x:c r="E2" s="72"/>
-      <x:c r="F2" s="72"/>
-      <x:c r="G2" s="72"/>
-      <x:c r="H2" s="72" t="str">
+      <x:c r="B2" s="112"/>
+      <x:c r="C2" s="112"/>
+      <x:c r="D2" s="112"/>
+      <x:c r="E2" s="112"/>
+      <x:c r="F2" s="112"/>
+      <x:c r="G2" s="112"/>
+      <x:c r="H2" s="112" t="str">
         <x:v>name</x:v>
       </x:c>
-      <x:c r="I2" s="72" t="str">
+      <x:c r="I2" s="112" t="str">
         <x:v>alias</x:v>
       </x:c>
-      <x:c r="J2" s="72" t="str">
+      <x:c r="J2" s="112" t="str">
         <x:v>value</x:v>
       </x:c>
-      <x:c r="K2" s="72" t="str">
+      <x:c r="K2" s="112" t="str">
         <x:v>comment</x:v>
       </x:c>
-      <x:c r="L2" s="72" t="str">
+      <x:c r="L2" s="112" t="str">
         <x:v>tags</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="75" t="str">
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="114" t="str">
         <x:v>##</x:v>
       </x:c>
-      <x:c r="B3" s="76" t="str">
+      <x:c r="B3" s="114" t="str">
         <x:v>完整枚举名</x:v>
       </x:c>
-      <x:c r="C3" s="76" t="str">
+      <x:c r="C3" s="114" t="str">
         <x:v>位标记</x:v>
       </x:c>
-      <x:c r="D3" s="76" t="str">
+      <x:c r="D3" s="114" t="str">
         <x:v>值唯一</x:v>
       </x:c>
-      <x:c r="E3" s="76" t="str">
+      <x:c r="E3" s="114" t="str">
         <x:v>分组</x:v>
       </x:c>
-      <x:c r="F3" s="76" t="str">
+      <x:c r="F3" s="114" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="G3" s="76" t="str">
+      <x:c r="G3" s="114" t="str">
         <x:v>标签</x:v>
       </x:c>
-      <x:c r="H3" s="76" t="str">
+      <x:c r="H3" s="114" t="str">
         <x:v>枚举项</x:v>
       </x:c>
-      <x:c r="I3" s="76" t="str">
+      <x:c r="I3" s="114" t="str">
         <x:v>别名</x:v>
       </x:c>
-      <x:c r="J3" s="76" t="str">
+      <x:c r="J3" s="114" t="str">
         <x:v>值</x:v>
       </x:c>
-      <x:c r="K3" s="76" t="str">
+      <x:c r="K3" s="114" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="L3" s="76" t="str">
+      <x:c r="L3" s="114" t="str">
         <x:v>标签</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="80"/>
-      <x:c r="B4" s="81" t="str">
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="101"/>
+      <x:c r="B4" s="101" t="str">
         <x:v>EResourceType</x:v>
       </x:c>
-      <x:c r="C4" s="82" t="b">
+      <x:c r="C4" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D4" s="82" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="81"/>
-      <x:c r="F4" s="81"/>
-      <x:c r="G4" s="81"/>
-      <x:c r="H4" s="81" t="str">
+      <x:c r="D4" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="101"/>
+      <x:c r="F4" s="101"/>
+      <x:c r="G4" s="101"/>
+      <x:c r="H4" s="101" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="I4" s="81"/>
-      <x:c r="J4" s="81" t="n">
+      <x:c r="I4" s="101"/>
+      <x:c r="J4" s="101" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K4" s="81" t="str">
+      <x:c r="K4" s="101" t="str">
         <x:v>未知</x:v>
       </x:c>
-      <x:c r="L4" s="81"/>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="99"/>
-      <x:c r="B5" s="99"/>
-      <x:c r="C5" s="99"/>
-      <x:c r="D5" s="99"/>
-      <x:c r="E5" s="99"/>
-      <x:c r="F5" s="99"/>
-      <x:c r="G5" s="99"/>
-      <x:c r="H5" s="99" t="str">
+      <x:c r="L4" s="101"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="101"/>
+      <x:c r="B5" s="101"/>
+      <x:c r="C5" s="101"/>
+      <x:c r="D5" s="101"/>
+      <x:c r="E5" s="101"/>
+      <x:c r="F5" s="101"/>
+      <x:c r="G5" s="101"/>
+      <x:c r="H5" s="101" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="I5" s="99"/>
-      <x:c r="J5" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K5" s="99" t="str">
+      <x:c r="I5" s="101"/>
+      <x:c r="J5" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K5" s="101" t="str">
         <x:v>ANI动画</x:v>
       </x:c>
-      <x:c r="L5" s="99"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="99"/>
-      <x:c r="B6" s="99"/>
-      <x:c r="C6" s="99"/>
-      <x:c r="D6" s="99"/>
-      <x:c r="E6" s="99"/>
-      <x:c r="F6" s="99"/>
-      <x:c r="G6" s="99"/>
-      <x:c r="H6" s="99" t="str">
+      <x:c r="L5" s="101"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="101"/>
+      <x:c r="B6" s="101"/>
+      <x:c r="C6" s="101"/>
+      <x:c r="D6" s="101"/>
+      <x:c r="E6" s="101"/>
+      <x:c r="F6" s="101"/>
+      <x:c r="G6" s="101"/>
+      <x:c r="H6" s="101" t="str">
         <x:v>Texture</x:v>
       </x:c>
-      <x:c r="I6" s="99"/>
-      <x:c r="J6" s="99" t="n">
+      <x:c r="I6" s="101"/>
+      <x:c r="J6" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K6" s="99" t="str">
+      <x:c r="K6" s="101" t="str">
         <x:v>纹理</x:v>
       </x:c>
-      <x:c r="L6" s="99"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="99"/>
-      <x:c r="B7" s="99"/>
-      <x:c r="C7" s="99"/>
-      <x:c r="D7" s="99"/>
-      <x:c r="E7" s="99"/>
-      <x:c r="F7" s="99"/>
-      <x:c r="G7" s="99"/>
-      <x:c r="H7" s="99" t="str">
+      <x:c r="L6" s="101"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="101"/>
+      <x:c r="B7" s="101"/>
+      <x:c r="C7" s="101"/>
+      <x:c r="D7" s="101"/>
+      <x:c r="E7" s="101"/>
+      <x:c r="F7" s="101"/>
+      <x:c r="G7" s="101"/>
+      <x:c r="H7" s="101" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="I7" s="99"/>
-      <x:c r="J7" s="99" t="n">
+      <x:c r="I7" s="101"/>
+      <x:c r="J7" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K7" s="99" t="str">
+      <x:c r="K7" s="101" t="str">
         <x:v>音频</x:v>
       </x:c>
-      <x:c r="L7" s="99"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="99"/>
-      <x:c r="B8" s="99"/>
-      <x:c r="C8" s="99"/>
-      <x:c r="D8" s="99"/>
-      <x:c r="E8" s="99"/>
-      <x:c r="F8" s="99"/>
-      <x:c r="G8" s="99"/>
-      <x:c r="H8" s="99" t="str">
+      <x:c r="L7" s="101"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="101"/>
+      <x:c r="B8" s="101"/>
+      <x:c r="C8" s="101"/>
+      <x:c r="D8" s="101"/>
+      <x:c r="E8" s="101"/>
+      <x:c r="F8" s="101"/>
+      <x:c r="G8" s="101"/>
+      <x:c r="H8" s="101" t="str">
         <x:v>MapData</x:v>
       </x:c>
-      <x:c r="I8" s="99"/>
-      <x:c r="J8" s="99" t="n">
+      <x:c r="I8" s="101"/>
+      <x:c r="J8" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K8" s="99" t="str">
+      <x:c r="K8" s="101" t="str">
         <x:v>地图数据</x:v>
       </x:c>
-      <x:c r="L8" s="99"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="99"/>
-      <x:c r="B9" s="99"/>
-      <x:c r="C9" s="99"/>
-      <x:c r="D9" s="99"/>
-      <x:c r="E9" s="99"/>
-      <x:c r="F9" s="99"/>
-      <x:c r="G9" s="99"/>
-      <x:c r="H9" s="99" t="str">
+      <x:c r="L8" s="101"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="101"/>
+      <x:c r="B9" s="101"/>
+      <x:c r="C9" s="101"/>
+      <x:c r="D9" s="101"/>
+      <x:c r="E9" s="101"/>
+      <x:c r="F9" s="101"/>
+      <x:c r="G9" s="101"/>
+      <x:c r="H9" s="101" t="str">
         <x:v>Binary</x:v>
       </x:c>
-      <x:c r="I9" s="99"/>
-      <x:c r="J9" s="99" t="n">
+      <x:c r="I9" s="101"/>
+      <x:c r="J9" s="101" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K9" s="99" t="str">
+      <x:c r="K9" s="101" t="str">
         <x:v>其他二进制</x:v>
       </x:c>
-      <x:c r="L9" s="99"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="99"/>
-      <x:c r="B10" s="99"/>
-      <x:c r="C10" s="99"/>
-      <x:c r="D10" s="99"/>
-      <x:c r="E10" s="99"/>
-      <x:c r="F10" s="99"/>
-      <x:c r="G10" s="99"/>
-      <x:c r="H10" s="99" t="str">
+      <x:c r="L9" s="101"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="101"/>
+      <x:c r="B10" s="101"/>
+      <x:c r="C10" s="101"/>
+      <x:c r="D10" s="101"/>
+      <x:c r="E10" s="101"/>
+      <x:c r="F10" s="101"/>
+      <x:c r="G10" s="101"/>
+      <x:c r="H10" s="101" t="str">
         <x:v>Prefab</x:v>
       </x:c>
-      <x:c r="I10" s="99"/>
-      <x:c r="J10" s="99" t="str">
+      <x:c r="I10" s="101"/>
+      <x:c r="J10" s="101" t="str">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K10" s="99" t="str">
+      <x:c r="K10" s="101" t="str">
         <x:v>Unity预制体</x:v>
       </x:c>
-      <x:c r="L10" s="99"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="99"/>
-      <x:c r="B11" s="99"/>
-      <x:c r="C11" s="99"/>
-      <x:c r="D11" s="99"/>
-      <x:c r="E11" s="99"/>
-      <x:c r="F11" s="99"/>
-      <x:c r="G11" s="99"/>
-      <x:c r="H11" s="99" t="str">
+      <x:c r="L10" s="101"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="101"/>
+      <x:c r="B11" s="101"/>
+      <x:c r="C11" s="101"/>
+      <x:c r="D11" s="101"/>
+      <x:c r="E11" s="101"/>
+      <x:c r="F11" s="101"/>
+      <x:c r="G11" s="101"/>
+      <x:c r="H11" s="101" t="str">
         <x:v>UnityAsset</x:v>
       </x:c>
-      <x:c r="I11" s="99"/>
-      <x:c r="J11" s="99" t="str">
+      <x:c r="I11" s="101"/>
+      <x:c r="J11" s="101" t="str">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K11" s="99" t="str">
+      <x:c r="K11" s="101" t="str">
         <x:v>其他Unity资产</x:v>
       </x:c>
-      <x:c r="L11" s="99"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="99"/>
-      <x:c r="B12" s="99" t="str">
+      <x:c r="L11" s="101"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="101"/>
+      <x:c r="B12" s="101" t="str">
         <x:v>EVisualCategory</x:v>
       </x:c>
-      <x:c r="C12" s="100" t="b">
+      <x:c r="C12" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D12" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E12" s="99"/>
-      <x:c r="F12" s="99"/>
-      <x:c r="G12" s="99"/>
-      <x:c r="H12" s="99" t="str">
+      <x:c r="D12" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E12" s="101"/>
+      <x:c r="F12" s="101"/>
+      <x:c r="G12" s="101"/>
+      <x:c r="H12" s="101" t="str">
         <x:v>Other</x:v>
       </x:c>
-      <x:c r="I12" s="99"/>
-      <x:c r="J12" s="99" t="n">
+      <x:c r="I12" s="101"/>
+      <x:c r="J12" s="101" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="99" t="str">
+      <x:c r="K12" s="101" t="str">
         <x:v>其他</x:v>
       </x:c>
-      <x:c r="L12" s="99"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="99"/>
-      <x:c r="B13" s="99"/>
-      <x:c r="C13" s="99"/>
-      <x:c r="D13" s="99"/>
-      <x:c r="E13" s="99"/>
-      <x:c r="F13" s="99"/>
-      <x:c r="G13" s="99"/>
-      <x:c r="H13" s="99" t="str">
+      <x:c r="L12" s="101"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="101"/>
+      <x:c r="B13" s="101"/>
+      <x:c r="C13" s="101"/>
+      <x:c r="D13" s="101"/>
+      <x:c r="E13" s="101"/>
+      <x:c r="F13" s="101"/>
+      <x:c r="G13" s="101"/>
+      <x:c r="H13" s="101" t="str">
         <x:v>Character</x:v>
       </x:c>
-      <x:c r="I13" s="99"/>
-      <x:c r="J13" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K13" s="99" t="str">
+      <x:c r="I13" s="101"/>
+      <x:c r="J13" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K13" s="101" t="str">
         <x:v>角色</x:v>
       </x:c>
-      <x:c r="L13" s="99"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="99"/>
-      <x:c r="B14" s="99"/>
-      <x:c r="C14" s="99"/>
-      <x:c r="D14" s="99"/>
-      <x:c r="E14" s="99"/>
-      <x:c r="F14" s="99"/>
-      <x:c r="G14" s="99"/>
-      <x:c r="H14" s="99" t="str">
+      <x:c r="L13" s="101"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="101"/>
+      <x:c r="B14" s="101"/>
+      <x:c r="C14" s="101"/>
+      <x:c r="D14" s="101"/>
+      <x:c r="E14" s="101"/>
+      <x:c r="F14" s="101"/>
+      <x:c r="G14" s="101"/>
+      <x:c r="H14" s="101" t="str">
         <x:v>Monster</x:v>
       </x:c>
-      <x:c r="I14" s="99"/>
-      <x:c r="J14" s="99" t="n">
+      <x:c r="I14" s="101"/>
+      <x:c r="J14" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K14" s="99" t="str">
+      <x:c r="K14" s="101" t="str">
         <x:v>怪物</x:v>
       </x:c>
-      <x:c r="L14" s="99"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="99"/>
-      <x:c r="B15" s="99"/>
-      <x:c r="C15" s="99"/>
-      <x:c r="D15" s="99"/>
-      <x:c r="E15" s="99"/>
-      <x:c r="F15" s="99"/>
-      <x:c r="G15" s="99"/>
-      <x:c r="H15" s="99" t="str">
+      <x:c r="L14" s="101"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="101"/>
+      <x:c r="B15" s="101"/>
+      <x:c r="C15" s="101"/>
+      <x:c r="D15" s="101"/>
+      <x:c r="E15" s="101"/>
+      <x:c r="F15" s="101"/>
+      <x:c r="G15" s="101"/>
+      <x:c r="H15" s="101" t="str">
         <x:v>Skill</x:v>
       </x:c>
-      <x:c r="I15" s="99"/>
-      <x:c r="J15" s="99" t="n">
+      <x:c r="I15" s="101"/>
+      <x:c r="J15" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K15" s="99" t="str">
+      <x:c r="K15" s="101" t="str">
         <x:v>技能</x:v>
       </x:c>
-      <x:c r="L15" s="99"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="99"/>
-      <x:c r="B16" s="99"/>
-      <x:c r="C16" s="99"/>
-      <x:c r="D16" s="99"/>
-      <x:c r="E16" s="99"/>
-      <x:c r="F16" s="99"/>
-      <x:c r="G16" s="99"/>
-      <x:c r="H16" s="99" t="str">
+      <x:c r="L15" s="101"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="101"/>
+      <x:c r="B16" s="101"/>
+      <x:c r="C16" s="101"/>
+      <x:c r="D16" s="101"/>
+      <x:c r="E16" s="101"/>
+      <x:c r="F16" s="101"/>
+      <x:c r="G16" s="101"/>
+      <x:c r="H16" s="101" t="str">
         <x:v>Map</x:v>
       </x:c>
-      <x:c r="I16" s="99"/>
-      <x:c r="J16" s="99" t="n">
+      <x:c r="I16" s="101"/>
+      <x:c r="J16" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K16" s="99" t="str">
+      <x:c r="K16" s="101" t="str">
         <x:v>地图</x:v>
       </x:c>
-      <x:c r="L16" s="99"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="99"/>
-      <x:c r="B17" s="99" t="str">
+      <x:c r="L16" s="101"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="101"/>
+      <x:c r="B17" s="101" t="str">
         <x:v>EAnimationAction</x:v>
       </x:c>
-      <x:c r="C17" s="100" t="b">
+      <x:c r="C17" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D17" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E17" s="99"/>
-      <x:c r="F17" s="99"/>
-      <x:c r="G17" s="99"/>
-      <x:c r="H17" s="99" t="str">
+      <x:c r="D17" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E17" s="101"/>
+      <x:c r="F17" s="101"/>
+      <x:c r="G17" s="101"/>
+      <x:c r="H17" s="101" t="str">
         <x:v>Unknown</x:v>
       </x:c>
-      <x:c r="I17" s="99"/>
-      <x:c r="J17" s="99" t="n">
+      <x:c r="I17" s="101"/>
+      <x:c r="J17" s="101" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="99" t="str">
+      <x:c r="K17" s="101" t="str">
         <x:v>尚未确认</x:v>
       </x:c>
-      <x:c r="L17" s="99"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="99"/>
-      <x:c r="B18" s="99"/>
-      <x:c r="C18" s="99"/>
-      <x:c r="D18" s="99"/>
-      <x:c r="E18" s="99"/>
-      <x:c r="F18" s="99"/>
-      <x:c r="G18" s="99"/>
-      <x:c r="H18" s="99" t="str">
+      <x:c r="L17" s="101"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="101"/>
+      <x:c r="B18" s="101"/>
+      <x:c r="C18" s="101"/>
+      <x:c r="D18" s="101"/>
+      <x:c r="E18" s="101"/>
+      <x:c r="F18" s="101"/>
+      <x:c r="G18" s="101"/>
+      <x:c r="H18" s="101" t="str">
         <x:v>Stand</x:v>
       </x:c>
-      <x:c r="I18" s="99"/>
-      <x:c r="J18" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K18" s="99" t="str">
+      <x:c r="I18" s="101"/>
+      <x:c r="J18" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K18" s="101" t="str">
         <x:v>待机：主角 fd，怪物 zd</x:v>
       </x:c>
-      <x:c r="L18" s="99"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="99"/>
-      <x:c r="B19" s="99"/>
-      <x:c r="C19" s="99"/>
-      <x:c r="D19" s="99"/>
-      <x:c r="E19" s="99"/>
-      <x:c r="F19" s="99"/>
-      <x:c r="G19" s="99"/>
-      <x:c r="H19" s="99" t="str">
+      <x:c r="L18" s="101"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="101"/>
+      <x:c r="B19" s="101"/>
+      <x:c r="C19" s="101"/>
+      <x:c r="D19" s="101"/>
+      <x:c r="E19" s="101"/>
+      <x:c r="F19" s="101"/>
+      <x:c r="G19" s="101"/>
+      <x:c r="H19" s="101" t="str">
         <x:v>Move</x:v>
       </x:c>
-      <x:c r="I19" s="99"/>
-      <x:c r="J19" s="99" t="n">
+      <x:c r="I19" s="101"/>
+      <x:c r="J19" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K19" s="99" t="str">
+      <x:c r="K19" s="101" t="str">
         <x:v>移动 pb</x:v>
       </x:c>
-      <x:c r="L19" s="99"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="99"/>
-      <x:c r="B20" s="99"/>
-      <x:c r="C20" s="99"/>
-      <x:c r="D20" s="99"/>
-      <x:c r="E20" s="99"/>
-      <x:c r="F20" s="99"/>
-      <x:c r="G20" s="99"/>
-      <x:c r="H20" s="99" t="str">
+      <x:c r="L19" s="101"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="101"/>
+      <x:c r="B20" s="101"/>
+      <x:c r="C20" s="101"/>
+      <x:c r="D20" s="101"/>
+      <x:c r="E20" s="101"/>
+      <x:c r="F20" s="101"/>
+      <x:c r="G20" s="101"/>
+      <x:c r="H20" s="101" t="str">
         <x:v>Unused</x:v>
       </x:c>
-      <x:c r="I20" s="99"/>
-      <x:c r="J20" s="99" t="n">
+      <x:c r="I20" s="101"/>
+      <x:c r="J20" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K20" s="99" t="str">
+      <x:c r="K20" s="101" t="str">
         <x:v>本轮不使用的动作</x:v>
       </x:c>
-      <x:c r="L20" s="99"/>
-    </x:row>
-    <x:row r="21" ht="28" customHeight="1">
-      <x:c r="A21" s="99"/>
-      <x:c r="B21" s="99"/>
-      <x:c r="C21" s="99"/>
-      <x:c r="D21" s="99"/>
-      <x:c r="E21" s="99"/>
-      <x:c r="F21" s="99"/>
-      <x:c r="G21" s="99"/>
-      <x:c r="H21" s="99" t="str">
+      <x:c r="L20" s="101"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="101"/>
+      <x:c r="B21" s="101"/>
+      <x:c r="C21" s="101"/>
+      <x:c r="D21" s="101"/>
+      <x:c r="E21" s="101"/>
+      <x:c r="F21" s="101"/>
+      <x:c r="G21" s="101"/>
+      <x:c r="H21" s="101" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="I21" s="99"/>
-      <x:c r="J21" s="99" t="n">
+      <x:c r="I21" s="101"/>
+      <x:c r="J21" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K21" s="99" t="str">
+      <x:c r="K21" s="101" t="str">
         <x:v>攻击 gj</x:v>
       </x:c>
-      <x:c r="L21" s="99"/>
-    </x:row>
-    <x:row r="22" ht="28" customHeight="1">
-      <x:c r="A22" s="99"/>
-      <x:c r="B22" s="99"/>
-      <x:c r="C22" s="99"/>
-      <x:c r="D22" s="99"/>
-      <x:c r="E22" s="99"/>
-      <x:c r="F22" s="99"/>
-      <x:c r="G22" s="99"/>
-      <x:c r="H22" s="99" t="str">
+      <x:c r="L21" s="101"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="101"/>
+      <x:c r="B22" s="101"/>
+      <x:c r="C22" s="101"/>
+      <x:c r="D22" s="101"/>
+      <x:c r="E22" s="101"/>
+      <x:c r="F22" s="101"/>
+      <x:c r="G22" s="101"/>
+      <x:c r="H22" s="101" t="str">
         <x:v>Hit</x:v>
       </x:c>
-      <x:c r="I22" s="99"/>
-      <x:c r="J22" s="99" t="n">
+      <x:c r="I22" s="101"/>
+      <x:c r="J22" s="101" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K22" s="99" t="str">
+      <x:c r="K22" s="101" t="str">
         <x:v>被击 bj</x:v>
       </x:c>
-      <x:c r="L22" s="99"/>
-    </x:row>
-    <x:row r="23" ht="28" customHeight="1">
-      <x:c r="A23" s="99"/>
-      <x:c r="B23" s="99"/>
-      <x:c r="C23" s="99"/>
-      <x:c r="D23" s="99"/>
-      <x:c r="E23" s="99"/>
-      <x:c r="F23" s="99"/>
-      <x:c r="G23" s="99"/>
-      <x:c r="H23" s="99" t="str">
+      <x:c r="L22" s="101"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="101"/>
+      <x:c r="B23" s="101"/>
+      <x:c r="C23" s="101"/>
+      <x:c r="D23" s="101"/>
+      <x:c r="E23" s="101"/>
+      <x:c r="F23" s="101"/>
+      <x:c r="G23" s="101"/>
+      <x:c r="H23" s="101" t="str">
         <x:v>Cast1</x:v>
       </x:c>
-      <x:c r="I23" s="99"/>
-      <x:c r="J23" s="99" t="n">
+      <x:c r="I23" s="101"/>
+      <x:c r="J23" s="101" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K23" s="99" t="str">
+      <x:c r="K23" s="101" t="str">
         <x:v>施法 sf1</x:v>
       </x:c>
-      <x:c r="L23" s="99"/>
-    </x:row>
-    <x:row r="24" ht="28" customHeight="1">
-      <x:c r="A24" s="99"/>
-      <x:c r="B24" s="99"/>
-      <x:c r="C24" s="99"/>
-      <x:c r="D24" s="99"/>
-      <x:c r="E24" s="99"/>
-      <x:c r="F24" s="99"/>
-      <x:c r="G24" s="99"/>
-      <x:c r="H24" s="99" t="str">
+      <x:c r="L23" s="101"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="101"/>
+      <x:c r="B24" s="101"/>
+      <x:c r="C24" s="101"/>
+      <x:c r="D24" s="101"/>
+      <x:c r="E24" s="101"/>
+      <x:c r="F24" s="101"/>
+      <x:c r="G24" s="101"/>
+      <x:c r="H24" s="101" t="str">
         <x:v>Cast2</x:v>
       </x:c>
-      <x:c r="I24" s="99"/>
-      <x:c r="J24" s="99" t="n">
+      <x:c r="I24" s="101"/>
+      <x:c r="J24" s="101" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K24" s="99" t="str">
+      <x:c r="K24" s="101" t="str">
         <x:v>施法 sf2</x:v>
       </x:c>
-      <x:c r="L24" s="99"/>
-    </x:row>
-    <x:row r="25" ht="28" customHeight="1">
-      <x:c r="A25" s="99"/>
-      <x:c r="B25" s="99"/>
-      <x:c r="C25" s="99"/>
-      <x:c r="D25" s="99"/>
-      <x:c r="E25" s="99"/>
-      <x:c r="F25" s="99"/>
-      <x:c r="G25" s="99"/>
-      <x:c r="H25" s="99" t="str">
+      <x:c r="L24" s="101"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="101"/>
+      <x:c r="B25" s="101"/>
+      <x:c r="C25" s="101"/>
+      <x:c r="D25" s="101"/>
+      <x:c r="E25" s="101"/>
+      <x:c r="F25" s="101"/>
+      <x:c r="G25" s="101"/>
+      <x:c r="H25" s="101" t="str">
         <x:v>Cast3</x:v>
       </x:c>
-      <x:c r="I25" s="99"/>
-      <x:c r="J25" s="99" t="n">
+      <x:c r="I25" s="101"/>
+      <x:c r="J25" s="101" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K25" s="99" t="str">
+      <x:c r="K25" s="101" t="str">
         <x:v>施法 sf3</x:v>
       </x:c>
-      <x:c r="L25" s="99"/>
-    </x:row>
-    <x:row r="26" ht="28" customHeight="1">
-      <x:c r="A26" s="99"/>
-      <x:c r="B26" s="99"/>
-      <x:c r="C26" s="99"/>
-      <x:c r="D26" s="99"/>
-      <x:c r="E26" s="99"/>
-      <x:c r="F26" s="99"/>
-      <x:c r="G26" s="99"/>
-      <x:c r="H26" s="99" t="str">
+      <x:c r="L25" s="101"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="101"/>
+      <x:c r="B26" s="101"/>
+      <x:c r="C26" s="101"/>
+      <x:c r="D26" s="101"/>
+      <x:c r="E26" s="101"/>
+      <x:c r="F26" s="101"/>
+      <x:c r="G26" s="101"/>
+      <x:c r="H26" s="101" t="str">
         <x:v>Cast4</x:v>
       </x:c>
-      <x:c r="I26" s="99"/>
-      <x:c r="J26" s="99" t="n">
+      <x:c r="I26" s="101"/>
+      <x:c r="J26" s="101" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K26" s="99" t="str">
+      <x:c r="K26" s="101" t="str">
         <x:v>施法 sf4</x:v>
       </x:c>
-      <x:c r="L26" s="99"/>
-    </x:row>
-    <x:row r="27" ht="28" customHeight="1">
-      <x:c r="A27" s="99"/>
-      <x:c r="B27" s="99"/>
-      <x:c r="C27" s="99"/>
-      <x:c r="D27" s="99"/>
-      <x:c r="E27" s="99"/>
-      <x:c r="F27" s="99"/>
-      <x:c r="G27" s="99"/>
-      <x:c r="H27" s="99" t="str">
+      <x:c r="L26" s="101"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="101"/>
+      <x:c r="B27" s="101"/>
+      <x:c r="C27" s="101"/>
+      <x:c r="D27" s="101"/>
+      <x:c r="E27" s="101"/>
+      <x:c r="F27" s="101"/>
+      <x:c r="G27" s="101"/>
+      <x:c r="H27" s="101" t="str">
         <x:v>Death</x:v>
       </x:c>
-      <x:c r="I27" s="99"/>
-      <x:c r="J27" s="99" t="n">
+      <x:c r="I27" s="101"/>
+      <x:c r="J27" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K27" s="99" t="str">
+      <x:c r="K27" s="101" t="str">
         <x:v>死亡 sw</x:v>
       </x:c>
-      <x:c r="L27" s="99"/>
-    </x:row>
-    <x:row r="28" ht="28" customHeight="1">
-      <x:c r="A28" s="99"/>
-      <x:c r="B28" s="99"/>
-      <x:c r="C28" s="99"/>
-      <x:c r="D28" s="99"/>
-      <x:c r="E28" s="99"/>
-      <x:c r="F28" s="99"/>
-      <x:c r="G28" s="99"/>
-      <x:c r="H28" s="99" t="str">
+      <x:c r="L27" s="101"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="101"/>
+      <x:c r="B28" s="101"/>
+      <x:c r="C28" s="101"/>
+      <x:c r="D28" s="101"/>
+      <x:c r="E28" s="101"/>
+      <x:c r="F28" s="101"/>
+      <x:c r="G28" s="101"/>
+      <x:c r="H28" s="101" t="str">
         <x:v>Projectile</x:v>
       </x:c>
-      <x:c r="I28" s="99"/>
-      <x:c r="J28" s="99" t="str">
+      <x:c r="I28" s="101"/>
+      <x:c r="J28" s="101" t="str">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K28" s="99" t="str">
+      <x:c r="K28" s="101" t="str">
         <x:v>弹丸飞行</x:v>
       </x:c>
-      <x:c r="L28" s="99"/>
-    </x:row>
-    <x:row r="29" ht="28" customHeight="1">
-      <x:c r="A29" s="99"/>
-      <x:c r="B29" s="99"/>
-      <x:c r="C29" s="99"/>
-      <x:c r="D29" s="99"/>
-      <x:c r="E29" s="99"/>
-      <x:c r="F29" s="99"/>
-      <x:c r="G29" s="99"/>
-      <x:c r="H29" s="99" t="str">
+      <x:c r="L28" s="101"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="101"/>
+      <x:c r="B29" s="101"/>
+      <x:c r="C29" s="101"/>
+      <x:c r="D29" s="101"/>
+      <x:c r="E29" s="101"/>
+      <x:c r="F29" s="101"/>
+      <x:c r="G29" s="101"/>
+      <x:c r="H29" s="101" t="str">
         <x:v>Impact</x:v>
       </x:c>
-      <x:c r="I29" s="99"/>
-      <x:c r="J29" s="99" t="str">
+      <x:c r="I29" s="101"/>
+      <x:c r="J29" s="101" t="str">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K29" s="99" t="str">
+      <x:c r="K29" s="101" t="str">
         <x:v>命中表现</x:v>
       </x:c>
-      <x:c r="L29" s="99"/>
-    </x:row>
-    <x:row r="30" ht="28" customHeight="1">
-      <x:c r="A30" s="99"/>
-      <x:c r="B30" s="99"/>
-      <x:c r="C30" s="99"/>
-      <x:c r="D30" s="99"/>
-      <x:c r="E30" s="99"/>
-      <x:c r="F30" s="99"/>
-      <x:c r="G30" s="99"/>
-      <x:c r="H30" s="99" t="str">
+      <x:c r="L29" s="101"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="101"/>
+      <x:c r="B30" s="101"/>
+      <x:c r="C30" s="101"/>
+      <x:c r="D30" s="101"/>
+      <x:c r="E30" s="101"/>
+      <x:c r="F30" s="101"/>
+      <x:c r="G30" s="101"/>
+      <x:c r="H30" s="101" t="str">
         <x:v>Area</x:v>
       </x:c>
-      <x:c r="I30" s="99"/>
-      <x:c r="J30" s="99" t="str">
+      <x:c r="I30" s="101"/>
+      <x:c r="J30" s="101" t="str">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K30" s="99" t="str">
+      <x:c r="K30" s="101" t="str">
         <x:v>目标位置范围表现</x:v>
       </x:c>
-      <x:c r="L30" s="99"/>
-    </x:row>
-    <x:row r="31" ht="28" customHeight="1">
-      <x:c r="A31" s="99"/>
-      <x:c r="B31" s="99" t="str">
+      <x:c r="L30" s="101"/>
+    </x:row>
+    <x:row r="31" ht="24" customHeight="1">
+      <x:c r="A31" s="101"/>
+      <x:c r="B31" s="101" t="str">
         <x:v>EPerformanceKind</x:v>
       </x:c>
-      <x:c r="C31" s="100" t="b">
+      <x:c r="C31" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D31" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E31" s="99"/>
-      <x:c r="F31" s="99"/>
-      <x:c r="G31" s="99"/>
-      <x:c r="H31" s="99" t="str">
+      <x:c r="D31" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="101"/>
+      <x:c r="F31" s="101"/>
+      <x:c r="G31" s="101"/>
+      <x:c r="H31" s="101" t="str">
         <x:v>SameMonster</x:v>
       </x:c>
-      <x:c r="I31" s="99"/>
-      <x:c r="J31" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K31" s="99" t="str">
+      <x:c r="I31" s="101"/>
+      <x:c r="J31" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K31" s="101" t="str">
         <x:v>同种怪物</x:v>
       </x:c>
-      <x:c r="L31" s="99"/>
-    </x:row>
-    <x:row r="32" ht="28" customHeight="1">
-      <x:c r="A32" s="99"/>
-      <x:c r="B32" s="99"/>
-      <x:c r="C32" s="99"/>
-      <x:c r="D32" s="99"/>
-      <x:c r="E32" s="99"/>
-      <x:c r="F32" s="99"/>
-      <x:c r="G32" s="99"/>
-      <x:c r="H32" s="99" t="str">
+      <x:c r="L31" s="101"/>
+    </x:row>
+    <x:row r="32" ht="24" customHeight="1">
+      <x:c r="A32" s="101"/>
+      <x:c r="B32" s="101"/>
+      <x:c r="C32" s="101"/>
+      <x:c r="D32" s="101"/>
+      <x:c r="E32" s="101"/>
+      <x:c r="F32" s="101"/>
+      <x:c r="G32" s="101"/>
+      <x:c r="H32" s="101" t="str">
         <x:v>MixedMonsters</x:v>
       </x:c>
-      <x:c r="I32" s="99"/>
-      <x:c r="J32" s="99" t="n">
+      <x:c r="I32" s="101"/>
+      <x:c r="J32" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K32" s="99" t="str">
+      <x:c r="K32" s="101" t="str">
         <x:v>混合怪物</x:v>
       </x:c>
-      <x:c r="L32" s="99"/>
-    </x:row>
-    <x:row r="33" ht="28" customHeight="1">
-      <x:c r="A33" s="99"/>
-      <x:c r="B33" s="99"/>
-      <x:c r="C33" s="99"/>
-      <x:c r="D33" s="99"/>
-      <x:c r="E33" s="99"/>
-      <x:c r="F33" s="99"/>
-      <x:c r="G33" s="99"/>
-      <x:c r="H33" s="99" t="str">
+      <x:c r="L32" s="101"/>
+    </x:row>
+    <x:row r="33" ht="24" customHeight="1">
+      <x:c r="A33" s="101"/>
+      <x:c r="B33" s="101"/>
+      <x:c r="C33" s="101"/>
+      <x:c r="D33" s="101"/>
+      <x:c r="E33" s="101"/>
+      <x:c r="F33" s="101"/>
+      <x:c r="G33" s="101"/>
+      <x:c r="H33" s="101" t="str">
         <x:v>MixedMonstersWithSkills</x:v>
       </x:c>
-      <x:c r="I33" s="99"/>
-      <x:c r="J33" s="99" t="n">
+      <x:c r="I33" s="101"/>
+      <x:c r="J33" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K33" s="99" t="str">
+      <x:c r="K33" s="101" t="str">
         <x:v>混合怪物与技能</x:v>
       </x:c>
-      <x:c r="L33" s="99"/>
-    </x:row>
-    <x:row r="34" ht="28" customHeight="1">
-      <x:c r="A34" s="99"/>
-      <x:c r="B34" s="99"/>
-      <x:c r="C34" s="99"/>
-      <x:c r="D34" s="99"/>
-      <x:c r="E34" s="99"/>
-      <x:c r="F34" s="99"/>
-      <x:c r="G34" s="99"/>
-      <x:c r="H34" s="99" t="str">
+      <x:c r="L33" s="101"/>
+    </x:row>
+    <x:row r="34" ht="24" customHeight="1">
+      <x:c r="A34" s="101"/>
+      <x:c r="B34" s="101"/>
+      <x:c r="C34" s="101"/>
+      <x:c r="D34" s="101"/>
+      <x:c r="E34" s="101"/>
+      <x:c r="F34" s="101"/>
+      <x:c r="G34" s="101"/>
+      <x:c r="H34" s="101" t="str">
         <x:v>Combat</x:v>
       </x:c>
-      <x:c r="I34" s="99"/>
-      <x:c r="J34" s="99" t="n">
+      <x:c r="I34" s="101"/>
+      <x:c r="J34" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K34" s="99" t="str">
+      <x:c r="K34" s="101" t="str">
         <x:v>完整战斗测试</x:v>
       </x:c>
-      <x:c r="L34" s="99"/>
-    </x:row>
-    <x:row r="35" ht="28" customHeight="1">
-      <x:c r="A35" s="99"/>
-      <x:c r="B35" s="99" t="str">
+      <x:c r="L34" s="101"/>
+    </x:row>
+    <x:row r="35" ht="24" customHeight="1">
+      <x:c r="A35" s="101"/>
+      <x:c r="B35" s="101" t="str">
         <x:v>EAttributeType</x:v>
       </x:c>
-      <x:c r="C35" s="100" t="b">
+      <x:c r="C35" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D35" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E35" s="99"/>
-      <x:c r="F35" s="99"/>
-      <x:c r="G35" s="99"/>
-      <x:c r="H35" s="99" t="str">
+      <x:c r="D35" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E35" s="101"/>
+      <x:c r="F35" s="101"/>
+      <x:c r="G35" s="101"/>
+      <x:c r="H35" s="101" t="str">
         <x:v>MaxHealth</x:v>
       </x:c>
-      <x:c r="I35" s="99"/>
-      <x:c r="J35" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K35" s="99" t="str">
+      <x:c r="I35" s="101"/>
+      <x:c r="J35" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K35" s="101" t="str">
         <x:v>最大生命</x:v>
       </x:c>
-      <x:c r="L35" s="99"/>
-    </x:row>
-    <x:row r="36" ht="28" customHeight="1">
-      <x:c r="A36" s="99"/>
-      <x:c r="B36" s="99"/>
-      <x:c r="C36" s="99"/>
-      <x:c r="D36" s="99"/>
-      <x:c r="E36" s="99"/>
-      <x:c r="F36" s="99"/>
-      <x:c r="G36" s="99"/>
-      <x:c r="H36" s="99" t="str">
+      <x:c r="L35" s="101"/>
+    </x:row>
+    <x:row r="36" ht="24" customHeight="1">
+      <x:c r="A36" s="101"/>
+      <x:c r="B36" s="101"/>
+      <x:c r="C36" s="101"/>
+      <x:c r="D36" s="101"/>
+      <x:c r="E36" s="101"/>
+      <x:c r="F36" s="101"/>
+      <x:c r="G36" s="101"/>
+      <x:c r="H36" s="101" t="str">
         <x:v>Attack</x:v>
       </x:c>
-      <x:c r="I36" s="99"/>
-      <x:c r="J36" s="99" t="n">
+      <x:c r="I36" s="101"/>
+      <x:c r="J36" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K36" s="99" t="str">
+      <x:c r="K36" s="101" t="str">
         <x:v>攻击</x:v>
       </x:c>
-      <x:c r="L36" s="99"/>
-    </x:row>
-    <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="99"/>
-      <x:c r="B37" s="99"/>
-      <x:c r="C37" s="99"/>
-      <x:c r="D37" s="99"/>
-      <x:c r="E37" s="99"/>
-      <x:c r="F37" s="99"/>
-      <x:c r="G37" s="99"/>
-      <x:c r="H37" s="99" t="str">
+      <x:c r="L36" s="101"/>
+    </x:row>
+    <x:row r="37" ht="24" customHeight="1">
+      <x:c r="A37" s="101"/>
+      <x:c r="B37" s="101"/>
+      <x:c r="C37" s="101"/>
+      <x:c r="D37" s="101"/>
+      <x:c r="E37" s="101"/>
+      <x:c r="F37" s="101"/>
+      <x:c r="G37" s="101"/>
+      <x:c r="H37" s="101" t="str">
         <x:v>Defense</x:v>
       </x:c>
-      <x:c r="I37" s="99"/>
-      <x:c r="J37" s="99" t="n">
+      <x:c r="I37" s="101"/>
+      <x:c r="J37" s="101" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K37" s="99" t="str">
+      <x:c r="K37" s="101" t="str">
         <x:v>防御</x:v>
       </x:c>
-      <x:c r="L37" s="99"/>
-    </x:row>
-    <x:row r="38" ht="28" customHeight="1">
-      <x:c r="A38" s="99"/>
-      <x:c r="B38" s="99"/>
-      <x:c r="C38" s="99"/>
-      <x:c r="D38" s="99"/>
-      <x:c r="E38" s="99"/>
-      <x:c r="F38" s="99"/>
-      <x:c r="G38" s="99"/>
-      <x:c r="H38" s="99" t="str">
+      <x:c r="L37" s="101"/>
+    </x:row>
+    <x:row r="38" ht="24" customHeight="1">
+      <x:c r="A38" s="101"/>
+      <x:c r="B38" s="101"/>
+      <x:c r="C38" s="101"/>
+      <x:c r="D38" s="101"/>
+      <x:c r="E38" s="101"/>
+      <x:c r="F38" s="101"/>
+      <x:c r="G38" s="101"/>
+      <x:c r="H38" s="101" t="str">
         <x:v>MoveSpeed</x:v>
       </x:c>
-      <x:c r="I38" s="99"/>
-      <x:c r="J38" s="99" t="n">
+      <x:c r="I38" s="101"/>
+      <x:c r="J38" s="101" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="K38" s="99" t="str">
+      <x:c r="K38" s="101" t="str">
         <x:v>移动速度</x:v>
       </x:c>
-      <x:c r="L38" s="99"/>
-    </x:row>
-    <x:row r="39" ht="28" customHeight="1">
-      <x:c r="A39" s="99"/>
-      <x:c r="B39" s="99"/>
-      <x:c r="C39" s="99"/>
-      <x:c r="D39" s="99"/>
-      <x:c r="E39" s="99"/>
-      <x:c r="F39" s="99"/>
-      <x:c r="G39" s="99"/>
-      <x:c r="H39" s="99" t="str">
+      <x:c r="L38" s="101"/>
+    </x:row>
+    <x:row r="39" ht="24" customHeight="1">
+      <x:c r="A39" s="101"/>
+      <x:c r="B39" s="101"/>
+      <x:c r="C39" s="101"/>
+      <x:c r="D39" s="101"/>
+      <x:c r="E39" s="101"/>
+      <x:c r="F39" s="101"/>
+      <x:c r="G39" s="101"/>
+      <x:c r="H39" s="101" t="str">
         <x:v>AttackSpeedMultiplier</x:v>
       </x:c>
-      <x:c r="I39" s="99"/>
-      <x:c r="J39" s="99" t="n">
+      <x:c r="I39" s="101"/>
+      <x:c r="J39" s="101" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="K39" s="99" t="str">
+      <x:c r="K39" s="101" t="str">
         <x:v>攻速倍率</x:v>
       </x:c>
-      <x:c r="L39" s="99"/>
-    </x:row>
-    <x:row r="40" ht="28" customHeight="1">
-      <x:c r="A40" s="99"/>
-      <x:c r="B40" s="99"/>
-      <x:c r="C40" s="99"/>
-      <x:c r="D40" s="99"/>
-      <x:c r="E40" s="99"/>
-      <x:c r="F40" s="99"/>
-      <x:c r="G40" s="99"/>
-      <x:c r="H40" s="99" t="str">
+      <x:c r="L39" s="101"/>
+    </x:row>
+    <x:row r="40" ht="24" customHeight="1">
+      <x:c r="A40" s="101"/>
+      <x:c r="B40" s="101"/>
+      <x:c r="C40" s="101"/>
+      <x:c r="D40" s="101"/>
+      <x:c r="E40" s="101"/>
+      <x:c r="F40" s="101"/>
+      <x:c r="G40" s="101"/>
+      <x:c r="H40" s="101" t="str">
         <x:v>DefenseParameter</x:v>
       </x:c>
-      <x:c r="I40" s="99"/>
-      <x:c r="J40" s="99" t="n">
+      <x:c r="I40" s="101"/>
+      <x:c r="J40" s="101" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="K40" s="99" t="str">
+      <x:c r="K40" s="101" t="str">
         <x:v>防御参数</x:v>
       </x:c>
-      <x:c r="L40" s="99"/>
-    </x:row>
-    <x:row r="41" ht="48" customHeight="1">
-      <x:c r="A41" s="99"/>
-      <x:c r="B41" s="99"/>
-      <x:c r="C41" s="99"/>
-      <x:c r="D41" s="99"/>
-      <x:c r="E41" s="99"/>
-      <x:c r="F41" s="99"/>
-      <x:c r="G41" s="99"/>
-      <x:c r="H41" s="99" t="str">
+      <x:c r="L40" s="101"/>
+    </x:row>
+    <x:row r="41" ht="24" customHeight="1">
+      <x:c r="A41" s="101"/>
+      <x:c r="B41" s="101"/>
+      <x:c r="C41" s="101"/>
+      <x:c r="D41" s="101"/>
+      <x:c r="E41" s="101"/>
+      <x:c r="F41" s="101"/>
+      <x:c r="G41" s="101"/>
+      <x:c r="H41" s="101" t="str">
         <x:v>Hit</x:v>
       </x:c>
-      <x:c r="I41" s="99"/>
-      <x:c r="J41" s="99" t="n">
+      <x:c r="I41" s="101"/>
+      <x:c r="J41" s="101" t="n">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="K41" s="99" t="str">
+      <x:c r="K41" s="101" t="str">
         <x:v>命中值</x:v>
       </x:c>
-      <x:c r="L41" s="99"/>
-    </x:row>
-    <x:row r="42" ht="28" customHeight="1">
-      <x:c r="A42" s="99"/>
-      <x:c r="B42" s="99"/>
-      <x:c r="C42" s="99"/>
-      <x:c r="D42" s="99"/>
-      <x:c r="E42" s="99"/>
-      <x:c r="F42" s="99"/>
-      <x:c r="G42" s="99"/>
-      <x:c r="H42" s="99" t="str">
+      <x:c r="L41" s="101"/>
+    </x:row>
+    <x:row r="42" ht="24" customHeight="1">
+      <x:c r="A42" s="101"/>
+      <x:c r="B42" s="101"/>
+      <x:c r="C42" s="101"/>
+      <x:c r="D42" s="101"/>
+      <x:c r="E42" s="101"/>
+      <x:c r="F42" s="101"/>
+      <x:c r="G42" s="101"/>
+      <x:c r="H42" s="101" t="str">
         <x:v>Evasion</x:v>
       </x:c>
-      <x:c r="I42" s="99"/>
-      <x:c r="J42" s="99" t="n">
+      <x:c r="I42" s="101"/>
+      <x:c r="J42" s="101" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="K42" s="99" t="str">
+      <x:c r="K42" s="101" t="str">
         <x:v>闪避值</x:v>
       </x:c>
-      <x:c r="L42" s="99"/>
-    </x:row>
-    <x:row r="43" ht="28" customHeight="1">
-      <x:c r="A43" s="99"/>
-      <x:c r="B43" s="99"/>
-      <x:c r="C43" s="99"/>
-      <x:c r="D43" s="99"/>
-      <x:c r="E43" s="99"/>
-      <x:c r="F43" s="99"/>
-      <x:c r="G43" s="99"/>
-      <x:c r="H43" s="99" t="str">
+      <x:c r="L42" s="101"/>
+    </x:row>
+    <x:row r="43" ht="24" customHeight="1">
+      <x:c r="A43" s="101"/>
+      <x:c r="B43" s="101"/>
+      <x:c r="C43" s="101"/>
+      <x:c r="D43" s="101"/>
+      <x:c r="E43" s="101"/>
+      <x:c r="F43" s="101"/>
+      <x:c r="G43" s="101"/>
+      <x:c r="H43" s="101" t="str">
         <x:v>HitParameter</x:v>
       </x:c>
-      <x:c r="I43" s="99"/>
-      <x:c r="J43" s="99" t="n">
+      <x:c r="I43" s="101"/>
+      <x:c r="J43" s="101" t="n">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="K43" s="99" t="str">
+      <x:c r="K43" s="101" t="str">
         <x:v>命中参数</x:v>
       </x:c>
-      <x:c r="L43" s="99"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="99"/>
-      <x:c r="B44" s="99"/>
-      <x:c r="C44" s="99"/>
-      <x:c r="D44" s="99"/>
-      <x:c r="E44" s="99"/>
-      <x:c r="F44" s="99"/>
-      <x:c r="G44" s="99"/>
-      <x:c r="H44" s="99" t="str">
+      <x:c r="L43" s="101"/>
+    </x:row>
+    <x:row r="44" ht="24" customHeight="1">
+      <x:c r="A44" s="101"/>
+      <x:c r="B44" s="101"/>
+      <x:c r="C44" s="101"/>
+      <x:c r="D44" s="101"/>
+      <x:c r="E44" s="101"/>
+      <x:c r="F44" s="101"/>
+      <x:c r="G44" s="101"/>
+      <x:c r="H44" s="101" t="str">
         <x:v>EvasionParameter</x:v>
       </x:c>
-      <x:c r="I44" s="99"/>
-      <x:c r="J44" s="99" t="n">
+      <x:c r="I44" s="101"/>
+      <x:c r="J44" s="101" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="K44" s="99" t="str">
+      <x:c r="K44" s="101" t="str">
         <x:v>闪避参数</x:v>
       </x:c>
-      <x:c r="L44" s="99"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="99"/>
-      <x:c r="B45" s="99"/>
-      <x:c r="C45" s="99"/>
-      <x:c r="D45" s="99"/>
-      <x:c r="E45" s="99"/>
-      <x:c r="F45" s="99"/>
-      <x:c r="G45" s="99"/>
-      <x:c r="H45" s="99" t="str">
+      <x:c r="L44" s="101"/>
+    </x:row>
+    <x:row r="45" ht="24" customHeight="1">
+      <x:c r="A45" s="101"/>
+      <x:c r="B45" s="101"/>
+      <x:c r="C45" s="101"/>
+      <x:c r="D45" s="101"/>
+      <x:c r="E45" s="101"/>
+      <x:c r="F45" s="101"/>
+      <x:c r="G45" s="101"/>
+      <x:c r="H45" s="101" t="str">
         <x:v>Critical</x:v>
       </x:c>
-      <x:c r="I45" s="99"/>
-      <x:c r="J45" s="99" t="n">
+      <x:c r="I45" s="101"/>
+      <x:c r="J45" s="101" t="n">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="K45" s="99" t="str">
+      <x:c r="K45" s="101" t="str">
         <x:v>暴击值</x:v>
       </x:c>
-      <x:c r="L45" s="99"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="99"/>
-      <x:c r="B46" s="99"/>
-      <x:c r="C46" s="99"/>
-      <x:c r="D46" s="99"/>
-      <x:c r="E46" s="99"/>
-      <x:c r="F46" s="99"/>
-      <x:c r="G46" s="99"/>
-      <x:c r="H46" s="99" t="str">
+      <x:c r="L45" s="101"/>
+    </x:row>
+    <x:row r="46" ht="24" customHeight="1">
+      <x:c r="A46" s="101"/>
+      <x:c r="B46" s="101"/>
+      <x:c r="C46" s="101"/>
+      <x:c r="D46" s="101"/>
+      <x:c r="E46" s="101"/>
+      <x:c r="F46" s="101"/>
+      <x:c r="G46" s="101"/>
+      <x:c r="H46" s="101" t="str">
         <x:v>CriticalResistance</x:v>
       </x:c>
-      <x:c r="I46" s="99"/>
-      <x:c r="J46" s="99" t="n">
+      <x:c r="I46" s="101"/>
+      <x:c r="J46" s="101" t="n">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K46" s="99" t="str">
+      <x:c r="K46" s="101" t="str">
         <x:v>抗暴值</x:v>
       </x:c>
-      <x:c r="L46" s="99"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="99"/>
-      <x:c r="B47" s="99"/>
-      <x:c r="C47" s="99"/>
-      <x:c r="D47" s="99"/>
-      <x:c r="E47" s="99"/>
-      <x:c r="F47" s="99"/>
-      <x:c r="G47" s="99"/>
-      <x:c r="H47" s="99" t="str">
+      <x:c r="L46" s="101"/>
+    </x:row>
+    <x:row r="47" ht="24" customHeight="1">
+      <x:c r="A47" s="101"/>
+      <x:c r="B47" s="101"/>
+      <x:c r="C47" s="101"/>
+      <x:c r="D47" s="101"/>
+      <x:c r="E47" s="101"/>
+      <x:c r="F47" s="101"/>
+      <x:c r="G47" s="101"/>
+      <x:c r="H47" s="101" t="str">
         <x:v>CriticalParameter</x:v>
       </x:c>
-      <x:c r="I47" s="99"/>
-      <x:c r="J47" s="99" t="n">
+      <x:c r="I47" s="101"/>
+      <x:c r="J47" s="101" t="n">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="K47" s="99" t="str">
+      <x:c r="K47" s="101" t="str">
         <x:v>暴击参数</x:v>
       </x:c>
-      <x:c r="L47" s="99"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="99"/>
-      <x:c r="B48" s="99"/>
-      <x:c r="C48" s="99"/>
-      <x:c r="D48" s="99"/>
-      <x:c r="E48" s="99"/>
-      <x:c r="F48" s="99"/>
-      <x:c r="G48" s="99"/>
-      <x:c r="H48" s="99" t="str">
+      <x:c r="L47" s="101"/>
+    </x:row>
+    <x:row r="48" ht="24" customHeight="1">
+      <x:c r="A48" s="101"/>
+      <x:c r="B48" s="101"/>
+      <x:c r="C48" s="101"/>
+      <x:c r="D48" s="101"/>
+      <x:c r="E48" s="101"/>
+      <x:c r="F48" s="101"/>
+      <x:c r="G48" s="101"/>
+      <x:c r="H48" s="101" t="str">
         <x:v>CriticalResistanceParameter</x:v>
       </x:c>
-      <x:c r="I48" s="99"/>
-      <x:c r="J48" s="99" t="n">
+      <x:c r="I48" s="101"/>
+      <x:c r="J48" s="101" t="n">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="K48" s="99" t="str">
+      <x:c r="K48" s="101" t="str">
         <x:v>抗暴参数</x:v>
       </x:c>
-      <x:c r="L48" s="99"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="99"/>
-      <x:c r="B49" s="99" t="str">
+      <x:c r="L48" s="101"/>
+    </x:row>
+    <x:row r="49" ht="24" customHeight="1">
+      <x:c r="A49" s="101"/>
+      <x:c r="B49" s="101"/>
+      <x:c r="C49" s="101"/>
+      <x:c r="D49" s="101"/>
+      <x:c r="E49" s="101"/>
+      <x:c r="F49" s="101"/>
+      <x:c r="G49" s="101"/>
+      <x:c r="H49" s="101" t="str">
+        <x:v>SkillRangeMultiplier</x:v>
+      </x:c>
+      <x:c r="I49" s="101"/>
+      <x:c r="J49" s="101" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K49" s="101" t="str">
+        <x:v>技能范围倍率</x:v>
+      </x:c>
+      <x:c r="L49" s="101"/>
+    </x:row>
+    <x:row r="50" ht="24" customHeight="1">
+      <x:c r="A50" s="101"/>
+      <x:c r="B50" s="101" t="str">
         <x:v>EAttributeValueKind</x:v>
       </x:c>
-      <x:c r="C49" s="100" t="b">
+      <x:c r="C50" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D49" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E49" s="99"/>
-      <x:c r="F49" s="99"/>
-      <x:c r="G49" s="99"/>
-      <x:c r="H49" s="99" t="str">
+      <x:c r="D50" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E50" s="101"/>
+      <x:c r="F50" s="101"/>
+      <x:c r="G50" s="101"/>
+      <x:c r="H50" s="101" t="str">
         <x:v>Integer</x:v>
       </x:c>
-      <x:c r="I49" s="99"/>
-      <x:c r="J49" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K49" s="99" t="str">
+      <x:c r="I50" s="101"/>
+      <x:c r="J50" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K50" s="101" t="str">
         <x:v>整数</x:v>
       </x:c>
-      <x:c r="L49" s="99"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="99"/>
-      <x:c r="B50" s="99"/>
-      <x:c r="C50" s="99"/>
-      <x:c r="D50" s="99"/>
-      <x:c r="E50" s="99"/>
-      <x:c r="F50" s="99"/>
-      <x:c r="G50" s="99"/>
-      <x:c r="H50" s="99" t="str">
+      <x:c r="L50" s="101"/>
+    </x:row>
+    <x:row r="51" ht="24" customHeight="1">
+      <x:c r="A51" s="101"/>
+      <x:c r="B51" s="101"/>
+      <x:c r="C51" s="101"/>
+      <x:c r="D51" s="101"/>
+      <x:c r="E51" s="101"/>
+      <x:c r="F51" s="101"/>
+      <x:c r="G51" s="101"/>
+      <x:c r="H51" s="101" t="str">
         <x:v>Real</x:v>
       </x:c>
-      <x:c r="I50" s="99"/>
-      <x:c r="J50" s="99" t="n">
+      <x:c r="I51" s="101"/>
+      <x:c r="J51" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K50" s="99" t="str">
+      <x:c r="K51" s="101" t="str">
         <x:v>实数</x:v>
       </x:c>
-      <x:c r="L50" s="99"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="99"/>
-      <x:c r="B51" s="99" t="str">
+      <x:c r="L51" s="101"/>
+    </x:row>
+    <x:row r="52" ht="24" customHeight="1">
+      <x:c r="A52" s="101"/>
+      <x:c r="B52" s="101" t="str">
         <x:v>ESkillDeliveryType</x:v>
       </x:c>
-      <x:c r="C51" s="100" t="b">
+      <x:c r="C52" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D51" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E51" s="99"/>
-      <x:c r="F51" s="99"/>
-      <x:c r="G51" s="99"/>
-      <x:c r="H51" s="99" t="str">
+      <x:c r="D52" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E52" s="101"/>
+      <x:c r="F52" s="101"/>
+      <x:c r="G52" s="101"/>
+      <x:c r="H52" s="101" t="str">
         <x:v>Projectile</x:v>
       </x:c>
-      <x:c r="I51" s="99"/>
-      <x:c r="J51" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K51" s="99" t="str">
+      <x:c r="I52" s="101"/>
+      <x:c r="J52" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K52" s="101" t="str">
         <x:v>直线弹丸</x:v>
       </x:c>
-      <x:c r="L51" s="99"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="99"/>
-      <x:c r="B52" s="99"/>
-      <x:c r="C52" s="99"/>
-      <x:c r="D52" s="99"/>
-      <x:c r="E52" s="99"/>
-      <x:c r="F52" s="99"/>
-      <x:c r="G52" s="99"/>
-      <x:c r="H52" s="99" t="str">
+      <x:c r="L52" s="101"/>
+    </x:row>
+    <x:row r="53" ht="24" customHeight="1">
+      <x:c r="A53" s="101"/>
+      <x:c r="B53" s="101"/>
+      <x:c r="C53" s="101"/>
+      <x:c r="D53" s="101"/>
+      <x:c r="E53" s="101"/>
+      <x:c r="F53" s="101"/>
+      <x:c r="G53" s="101"/>
+      <x:c r="H53" s="101" t="str">
         <x:v>Melee</x:v>
       </x:c>
-      <x:c r="I52" s="99"/>
-      <x:c r="J52" s="99" t="n">
+      <x:c r="I53" s="101"/>
+      <x:c r="J53" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K52" s="99" t="str">
+      <x:c r="K53" s="101" t="str">
         <x:v>近战</x:v>
       </x:c>
-      <x:c r="L52" s="99"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="99"/>
-      <x:c r="B53" s="99"/>
-      <x:c r="C53" s="99"/>
-      <x:c r="D53" s="99"/>
-      <x:c r="E53" s="99"/>
-      <x:c r="F53" s="99"/>
-      <x:c r="G53" s="99"/>
-      <x:c r="H53" s="99" t="str">
+      <x:c r="L53" s="101"/>
+    </x:row>
+    <x:row r="54" ht="24" customHeight="1">
+      <x:c r="A54" s="101"/>
+      <x:c r="B54" s="101"/>
+      <x:c r="C54" s="101"/>
+      <x:c r="D54" s="101"/>
+      <x:c r="E54" s="101"/>
+      <x:c r="F54" s="101"/>
+      <x:c r="G54" s="101"/>
+      <x:c r="H54" s="101" t="str">
         <x:v>TargetArea</x:v>
       </x:c>
-      <x:c r="I53" s="99"/>
-      <x:c r="J53" s="99" t="str">
+      <x:c r="I54" s="101"/>
+      <x:c r="J54" s="101" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K53" s="99" t="str">
+      <x:c r="K54" s="101" t="str">
         <x:v>目标位置群体释放</x:v>
       </x:c>
-      <x:c r="L53" s="99"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="99"/>
-      <x:c r="B54" s="99" t="str">
+      <x:c r="L54" s="101"/>
+    </x:row>
+    <x:row r="55" ht="24" customHeight="1">
+      <x:c r="A55" s="101"/>
+      <x:c r="B55" s="101" t="str">
         <x:v>ETestHealthPolicy</x:v>
       </x:c>
-      <x:c r="C54" s="100" t="b">
+      <x:c r="C55" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D54" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E54" s="99"/>
-      <x:c r="F54" s="99"/>
-      <x:c r="G54" s="99"/>
-      <x:c r="H54" s="99" t="str">
+      <x:c r="D55" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E55" s="101"/>
+      <x:c r="F55" s="101"/>
+      <x:c r="G55" s="101"/>
+      <x:c r="H55" s="101" t="str">
         <x:v>Normal</x:v>
       </x:c>
-      <x:c r="I54" s="99"/>
-      <x:c r="J54" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K54" s="99" t="str">
+      <x:c r="I55" s="101"/>
+      <x:c r="J55" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K55" s="101" t="str">
         <x:v>正常生命</x:v>
       </x:c>
-      <x:c r="L54" s="99"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="99"/>
-      <x:c r="B55" s="99"/>
-      <x:c r="C55" s="99"/>
-      <x:c r="D55" s="99"/>
-      <x:c r="E55" s="99"/>
-      <x:c r="F55" s="99"/>
-      <x:c r="G55" s="99"/>
-      <x:c r="H55" s="99" t="str">
+      <x:c r="L55" s="101"/>
+    </x:row>
+    <x:row r="56" ht="24" customHeight="1">
+      <x:c r="A56" s="101"/>
+      <x:c r="B56" s="101"/>
+      <x:c r="C56" s="101"/>
+      <x:c r="D56" s="101"/>
+      <x:c r="E56" s="101"/>
+      <x:c r="F56" s="101"/>
+      <x:c r="G56" s="101"/>
+      <x:c r="H56" s="101" t="str">
         <x:v>RestoreAfterDamage</x:v>
       </x:c>
-      <x:c r="I55" s="99"/>
-      <x:c r="J55" s="99" t="n">
+      <x:c r="I56" s="101"/>
+      <x:c r="J56" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K55" s="99" t="str">
+      <x:c r="K56" s="101" t="str">
         <x:v>结算正数扣血后恢复测试玩家生命</x:v>
       </x:c>
-      <x:c r="L55" s="99"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="99"/>
-      <x:c r="B56" s="99" t="str">
+      <x:c r="L56" s="101"/>
+    </x:row>
+    <x:row r="57" ht="24" customHeight="1">
+      <x:c r="A57" s="101"/>
+      <x:c r="B57" s="101" t="str">
         <x:v>ETestInputPolicy</x:v>
       </x:c>
-      <x:c r="C56" s="100" t="b">
+      <x:c r="C57" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D56" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E56" s="99"/>
-      <x:c r="F56" s="99"/>
-      <x:c r="G56" s="99"/>
-      <x:c r="H56" s="99" t="str">
+      <x:c r="D57" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E57" s="101"/>
+      <x:c r="F57" s="101"/>
+      <x:c r="G57" s="101"/>
+      <x:c r="H57" s="101" t="str">
         <x:v>Manual</x:v>
       </x:c>
-      <x:c r="I56" s="99"/>
-      <x:c r="J56" s="99" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K56" s="99" t="str">
+      <x:c r="I57" s="101"/>
+      <x:c r="J57" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K57" s="101" t="str">
         <x:v>玩家操作</x:v>
       </x:c>
-      <x:c r="L56" s="99"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="99"/>
-      <x:c r="B57" s="99"/>
-      <x:c r="C57" s="99"/>
-      <x:c r="D57" s="99"/>
-      <x:c r="E57" s="99"/>
-      <x:c r="F57" s="99"/>
-      <x:c r="G57" s="99"/>
-      <x:c r="H57" s="99" t="str">
+      <x:c r="L57" s="101"/>
+    </x:row>
+    <x:row r="58" ht="24" customHeight="1">
+      <x:c r="A58" s="101"/>
+      <x:c r="B58" s="101"/>
+      <x:c r="C58" s="101"/>
+      <x:c r="D58" s="101"/>
+      <x:c r="E58" s="101"/>
+      <x:c r="F58" s="101"/>
+      <x:c r="G58" s="101"/>
+      <x:c r="H58" s="101" t="str">
         <x:v>Stationary</x:v>
       </x:c>
-      <x:c r="I57" s="99"/>
-      <x:c r="J57" s="99" t="n">
+      <x:c r="I58" s="101"/>
+      <x:c r="J58" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K57" s="99" t="str">
+      <x:c r="K58" s="101" t="str">
         <x:v>玩家静止</x:v>
       </x:c>
-      <x:c r="L57" s="99"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="99"/>
-      <x:c r="B58" s="99" t="str">
+      <x:c r="L58" s="101"/>
+    </x:row>
+    <x:row r="59" ht="24" customHeight="1">
+      <x:c r="A59" s="101"/>
+      <x:c r="B59" s="101" t="str">
         <x:v>EMovementType</x:v>
       </x:c>
-      <x:c r="C58" s="100" t="b">
+      <x:c r="C59" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D58" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E58" s="99"/>
-      <x:c r="F58" s="99" t="str">
+      <x:c r="D59" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E59" s="101"/>
+      <x:c r="F59" s="101" t="str">
         <x:v>单位移动分类</x:v>
       </x:c>
-      <x:c r="G58" s="99"/>
-      <x:c r="H58" s="99" t="str">
+      <x:c r="G59" s="101"/>
+      <x:c r="H59" s="101" t="str">
         <x:v>Ground</x:v>
       </x:c>
-      <x:c r="I58" s="99"/>
-      <x:c r="J58" s="99" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K58" s="99" t="str">
+      <x:c r="I59" s="101"/>
+      <x:c r="J59" s="101" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K59" s="101" t="str">
         <x:v>地面</x:v>
       </x:c>
-      <x:c r="L58" s="99"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="99"/>
-      <x:c r="B59" s="99"/>
-      <x:c r="C59" s="99"/>
-      <x:c r="D59" s="99"/>
-      <x:c r="E59" s="99"/>
-      <x:c r="F59" s="99"/>
-      <x:c r="G59" s="99"/>
-      <x:c r="H59" s="99" t="str">
+      <x:c r="L59" s="101"/>
+    </x:row>
+    <x:row r="60" ht="24" customHeight="1">
+      <x:c r="A60" s="101"/>
+      <x:c r="B60" s="101"/>
+      <x:c r="C60" s="101"/>
+      <x:c r="D60" s="101"/>
+      <x:c r="E60" s="101"/>
+      <x:c r="F60" s="101"/>
+      <x:c r="G60" s="101"/>
+      <x:c r="H60" s="101" t="str">
         <x:v>Flying</x:v>
       </x:c>
-      <x:c r="I59" s="99"/>
-      <x:c r="J59" s="99" t="str">
+      <x:c r="I60" s="101"/>
+      <x:c r="J60" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K59" s="99" t="str">
+      <x:c r="K60" s="101" t="str">
         <x:v>飞行</x:v>
       </x:c>
-      <x:c r="L59" s="99"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="99"/>
-      <x:c r="B60" s="99" t="str">
+      <x:c r="L60" s="101"/>
+    </x:row>
+    <x:row r="61" ht="24" customHeight="1">
+      <x:c r="A61" s="101"/>
+      <x:c r="B61" s="101" t="str">
         <x:v>EUpgradeOptionType</x:v>
       </x:c>
-      <x:c r="C60" s="100" t="b">
+      <x:c r="C61" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D60" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E60" s="99"/>
-      <x:c r="F60" s="99" t="str">
+      <x:c r="D61" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E61" s="101"/>
+      <x:c r="F61" s="101" t="str">
         <x:v>局内升级选项类型</x:v>
       </x:c>
-      <x:c r="G60" s="99"/>
-      <x:c r="H60" s="99" t="str">
+      <x:c r="G61" s="101"/>
+      <x:c r="H61" s="101" t="str">
         <x:v>SkillUnlock</x:v>
       </x:c>
-      <x:c r="I60" s="99"/>
-      <x:c r="J60" s="99" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K60" s="99" t="str">
+      <x:c r="I61" s="101"/>
+      <x:c r="J61" s="101" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K61" s="101" t="str">
         <x:v>解锁技能</x:v>
       </x:c>
-      <x:c r="L60" s="99"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="99"/>
-      <x:c r="B61" s="99"/>
-      <x:c r="C61" s="99"/>
-      <x:c r="D61" s="99"/>
-      <x:c r="E61" s="99"/>
-      <x:c r="F61" s="99"/>
-      <x:c r="G61" s="99"/>
-      <x:c r="H61" s="99" t="str">
+      <x:c r="L61" s="101"/>
+    </x:row>
+    <x:row r="62" ht="24" customHeight="1">
+      <x:c r="A62" s="101"/>
+      <x:c r="B62" s="101"/>
+      <x:c r="C62" s="101"/>
+      <x:c r="D62" s="101"/>
+      <x:c r="E62" s="101"/>
+      <x:c r="F62" s="101"/>
+      <x:c r="G62" s="101"/>
+      <x:c r="H62" s="101" t="str">
         <x:v>Attribute</x:v>
       </x:c>
-      <x:c r="I61" s="99"/>
-      <x:c r="J61" s="99" t="str">
+      <x:c r="I62" s="101"/>
+      <x:c r="J62" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K61" s="99" t="str">
+      <x:c r="K62" s="101" t="str">
         <x:v>属性强化</x:v>
       </x:c>
-      <x:c r="L61" s="99"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="99"/>
-      <x:c r="B62" s="99"/>
-      <x:c r="C62" s="99"/>
-      <x:c r="D62" s="99"/>
-      <x:c r="E62" s="99"/>
-      <x:c r="F62" s="99"/>
-      <x:c r="G62" s="99"/>
-      <x:c r="H62" s="99" t="str">
+      <x:c r="L62" s="101"/>
+    </x:row>
+    <x:row r="63" ht="24" customHeight="1">
+      <x:c r="A63" s="101"/>
+      <x:c r="B63" s="101"/>
+      <x:c r="C63" s="101"/>
+      <x:c r="D63" s="101"/>
+      <x:c r="E63" s="101"/>
+      <x:c r="F63" s="101"/>
+      <x:c r="G63" s="101"/>
+      <x:c r="H63" s="101" t="str">
         <x:v>Heal</x:v>
       </x:c>
-      <x:c r="I62" s="99"/>
-      <x:c r="J62" s="99" t="str">
+      <x:c r="I63" s="101"/>
+      <x:c r="J63" s="101" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K62" s="99" t="str">
+      <x:c r="K63" s="101" t="str">
         <x:v>立即恢复</x:v>
       </x:c>
-      <x:c r="L62" s="99"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="99"/>
-      <x:c r="B63" s="99" t="str">
+      <x:c r="L63" s="101"/>
+    </x:row>
+    <x:row r="64" ht="24" customHeight="1">
+      <x:c r="A64" s="101"/>
+      <x:c r="B64" s="101"/>
+      <x:c r="C64" s="101"/>
+      <x:c r="D64" s="101"/>
+      <x:c r="E64" s="101"/>
+      <x:c r="F64" s="101"/>
+      <x:c r="G64" s="101"/>
+      <x:c r="H64" s="101" t="str">
+        <x:v>RunWeapon</x:v>
+      </x:c>
+      <x:c r="I64" s="101"/>
+      <x:c r="J64" s="101" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="K64" s="101" t="str">
+        <x:v>获得武器或升星</x:v>
+      </x:c>
+      <x:c r="L64" s="101"/>
+    </x:row>
+    <x:row r="65" ht="24" customHeight="1">
+      <x:c r="A65" s="101"/>
+      <x:c r="B65" s="101"/>
+      <x:c r="C65" s="101"/>
+      <x:c r="D65" s="101"/>
+      <x:c r="E65" s="101"/>
+      <x:c r="F65" s="101"/>
+      <x:c r="G65" s="101"/>
+      <x:c r="H65" s="101" t="str">
+        <x:v>RunPassive</x:v>
+      </x:c>
+      <x:c r="I65" s="101"/>
+      <x:c r="J65" s="101" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="K65" s="101" t="str">
+        <x:v>获得被动或升级</x:v>
+      </x:c>
+      <x:c r="L65" s="101"/>
+    </x:row>
+    <x:row r="66" ht="24" customHeight="1">
+      <x:c r="A66" s="101"/>
+      <x:c r="B66" s="101" t="str">
         <x:v>EAttributeModifyOperation</x:v>
       </x:c>
-      <x:c r="C63" s="100" t="b">
+      <x:c r="C66" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D63" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E63" s="99"/>
-      <x:c r="F63" s="99" t="str">
+      <x:c r="D66" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E66" s="101"/>
+      <x:c r="F66" s="101" t="str">
         <x:v>局内属性修改操作</x:v>
       </x:c>
-      <x:c r="G63" s="99"/>
-      <x:c r="H63" s="99" t="str">
+      <x:c r="G66" s="101"/>
+      <x:c r="H66" s="101" t="str">
         <x:v>Add</x:v>
       </x:c>
-      <x:c r="I63" s="99"/>
-      <x:c r="J63" s="99" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K63" s="99" t="str">
+      <x:c r="I66" s="101"/>
+      <x:c r="J66" s="101" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K66" s="101" t="str">
         <x:v>固定值相加</x:v>
       </x:c>
-      <x:c r="L63" s="99"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="99"/>
-      <x:c r="B64" s="99"/>
-      <x:c r="C64" s="99"/>
-      <x:c r="D64" s="99"/>
-      <x:c r="E64" s="99"/>
-      <x:c r="F64" s="99"/>
-      <x:c r="G64" s="99"/>
-      <x:c r="H64" s="99" t="str">
+      <x:c r="L66" s="101"/>
+    </x:row>
+    <x:row r="67" ht="24" customHeight="1">
+      <x:c r="A67" s="101"/>
+      <x:c r="B67" s="101"/>
+      <x:c r="C67" s="101"/>
+      <x:c r="D67" s="101"/>
+      <x:c r="E67" s="101"/>
+      <x:c r="F67" s="101"/>
+      <x:c r="G67" s="101"/>
+      <x:c r="H67" s="101" t="str">
         <x:v>AddPercent</x:v>
       </x:c>
-      <x:c r="I64" s="99"/>
-      <x:c r="J64" s="99" t="str">
+      <x:c r="I67" s="101"/>
+      <x:c r="J67" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K64" s="99" t="str">
+      <x:c r="K67" s="101" t="str">
         <x:v>基础值百分比相加</x:v>
       </x:c>
-      <x:c r="L64" s="99"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="99"/>
-      <x:c r="B65" s="99"/>
-      <x:c r="C65" s="99"/>
-      <x:c r="D65" s="99"/>
-      <x:c r="E65" s="99"/>
-      <x:c r="F65" s="99"/>
-      <x:c r="G65" s="99"/>
-      <x:c r="H65" s="99" t="str">
+      <x:c r="L67" s="101"/>
+    </x:row>
+    <x:row r="68" ht="24" customHeight="1">
+      <x:c r="A68" s="101"/>
+      <x:c r="B68" s="101"/>
+      <x:c r="C68" s="101"/>
+      <x:c r="D68" s="101"/>
+      <x:c r="E68" s="101"/>
+      <x:c r="F68" s="101"/>
+      <x:c r="G68" s="101"/>
+      <x:c r="H68" s="101" t="str">
         <x:v>Multiply</x:v>
       </x:c>
-      <x:c r="I65" s="99"/>
-      <x:c r="J65" s="99" t="str">
+      <x:c r="I68" s="101"/>
+      <x:c r="J68" s="101" t="str">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="K65" s="99" t="str">
+      <x:c r="K68" s="101" t="str">
         <x:v>最终值相乘</x:v>
       </x:c>
-      <x:c r="L65" s="99"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="99"/>
-      <x:c r="B66" s="99" t="str">
+      <x:c r="L68" s="101"/>
+    </x:row>
+    <x:row r="69" ht="24" customHeight="1">
+      <x:c r="A69" s="101"/>
+      <x:c r="B69" s="101" t="str">
         <x:v>ERunResultType</x:v>
       </x:c>
-      <x:c r="C66" s="100" t="b">
+      <x:c r="C69" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D66" s="100" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E66" s="99"/>
-      <x:c r="F66" s="99" t="str">
+      <x:c r="D69" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E69" s="101"/>
+      <x:c r="F69" s="101" t="str">
         <x:v>单局结算结果</x:v>
       </x:c>
-      <x:c r="G66" s="99"/>
-      <x:c r="H66" s="99" t="str">
+      <x:c r="G69" s="101"/>
+      <x:c r="H69" s="101" t="str">
         <x:v>Victory</x:v>
       </x:c>
-      <x:c r="I66" s="99"/>
-      <x:c r="J66" s="99" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K66" s="99" t="str">
+      <x:c r="I69" s="101"/>
+      <x:c r="J69" s="101" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K69" s="101" t="str">
         <x:v>胜利</x:v>
       </x:c>
-      <x:c r="L66" s="99"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="99"/>
-      <x:c r="B67" s="99"/>
-      <x:c r="C67" s="99"/>
-      <x:c r="D67" s="99"/>
-      <x:c r="E67" s="99"/>
-      <x:c r="F67" s="99"/>
-      <x:c r="G67" s="99"/>
-      <x:c r="H67" s="99" t="str">
+      <x:c r="L69" s="101"/>
+    </x:row>
+    <x:row r="70" ht="24" customHeight="1">
+      <x:c r="A70" s="101"/>
+      <x:c r="B70" s="101"/>
+      <x:c r="C70" s="101"/>
+      <x:c r="D70" s="101"/>
+      <x:c r="E70" s="101"/>
+      <x:c r="F70" s="101"/>
+      <x:c r="G70" s="101"/>
+      <x:c r="H70" s="101" t="str">
         <x:v>Defeat</x:v>
       </x:c>
-      <x:c r="I67" s="99"/>
-      <x:c r="J67" s="99" t="str">
+      <x:c r="I70" s="101"/>
+      <x:c r="J70" s="101" t="str">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K67" s="99" t="str">
+      <x:c r="K70" s="101" t="str">
         <x:v>失败</x:v>
       </x:c>
-      <x:c r="L67" s="99"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69"/>
-      <x:c r="B69" t="str">
+      <x:c r="L70" s="101"/>
+    </x:row>
+    <x:row r="71" ht="24" customHeight="1">
+      <x:c r="A71" s="101"/>
+      <x:c r="B71" s="101"/>
+      <x:c r="C71" s="101"/>
+      <x:c r="D71" s="101"/>
+      <x:c r="E71" s="101"/>
+      <x:c r="F71" s="101"/>
+      <x:c r="G71" s="101"/>
+      <x:c r="H71" s="101"/>
+      <x:c r="I71" s="101"/>
+      <x:c r="J71" s="101"/>
+      <x:c r="K71" s="101"/>
+      <x:c r="L71" s="101"/>
+    </x:row>
+    <x:row r="72" ht="24" customHeight="1">
+      <x:c r="A72" s="101"/>
+      <x:c r="B72" s="101" t="str">
         <x:v>EUnitCollisionShape</x:v>
       </x:c>
-      <x:c r="C69" s="1" t="b">
+      <x:c r="C72" s="102" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="D69" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E69"/>
-      <x:c r="F69" t="str">
+      <x:c r="D72" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E72" s="101"/>
+      <x:c r="F72" s="101" t="str">
         <x:v>单位统一碰撞形状</x:v>
       </x:c>
-      <x:c r="G69"/>
-      <x:c r="H69" t="str">
+      <x:c r="G72" s="101"/>
+      <x:c r="H72" s="101" t="str">
         <x:v>VerticalCapsule</x:v>
+      </x:c>
+      <x:c r="I72" s="101"/>
+      <x:c r="J72" s="101"/>
+      <x:c r="K72" s="101"/>
+      <x:c r="L72" s="101"/>
+    </x:row>
+    <x:row r="73" ht="24" customHeight="1">
+      <x:c r="A73" s="101"/>
+      <x:c r="B73" s="101" t="str">
+        <x:v>EResourcePackage</x:v>
+      </x:c>
+      <x:c r="C73" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D73" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E73" s="101"/>
+      <x:c r="F73" s="101" t="str">
+        <x:v>资源包归属</x:v>
+      </x:c>
+      <x:c r="G73" s="101"/>
+      <x:c r="H73" s="101" t="str">
+        <x:v>Raw</x:v>
+      </x:c>
+      <x:c r="I73" s="101"/>
+      <x:c r="J73" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K73" s="101" t="str">
+        <x:v>原始字节包</x:v>
+      </x:c>
+      <x:c r="L73" s="101"/>
+    </x:row>
+    <x:row r="74" ht="24" customHeight="1">
+      <x:c r="A74" s="101"/>
+      <x:c r="B74" s="101"/>
+      <x:c r="C74" s="101"/>
+      <x:c r="D74" s="101"/>
+      <x:c r="E74" s="101"/>
+      <x:c r="F74" s="101"/>
+      <x:c r="G74" s="101"/>
+      <x:c r="H74" s="101" t="str">
+        <x:v>GameAsset</x:v>
+      </x:c>
+      <x:c r="I74" s="101"/>
+      <x:c r="J74" s="101" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K74" s="101" t="str">
+        <x:v>Unity资产包</x:v>
+      </x:c>
+      <x:c r="L74" s="101"/>
+    </x:row>
+    <x:row r="75" ht="24" customHeight="1">
+      <x:c r="A75"/>
+      <x:c r="B75" t="str">
+        <x:v>EUpgradeExhaustionPolicy</x:v>
+      </x:c>
+      <x:c r="C75" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D75" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E75"/>
+      <x:c r="F75" t="str">
+        <x:v>升级候选耗尽策略</x:v>
+      </x:c>
+      <x:c r="G75"/>
+      <x:c r="H75" t="str">
+        <x:v>ReduceOfferCount</x:v>
+      </x:c>
+      <x:c r="I75"/>
+      <x:c r="J75" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K75" t="str">
+        <x:v>按剩余合法候选降量展示</x:v>
+      </x:c>
+      <x:c r="L75"/>
+    </x:row>
+    <x:row r="76" ht="24" customHeight="1">
+      <x:c r="A76"/>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
+      <x:c r="E76"/>
+      <x:c r="F76"/>
+      <x:c r="G76"/>
+      <x:c r="H76" t="str">
+        <x:v>FallbackPool</x:v>
+      </x:c>
+      <x:c r="I76"/>
+      <x:c r="J76" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K76" t="str">
+        <x:v>切换后备池重新筛选</x:v>
+      </x:c>
+      <x:c r="L76"/>
+    </x:row>
+    <x:row r="77" ht="24" customHeight="1">
+      <x:c r="A77"/>
+      <x:c r="B77"/>
+      <x:c r="C77"/>
+      <x:c r="D77"/>
+      <x:c r="E77"/>
+      <x:c r="F77"/>
+      <x:c r="G77"/>
+      <x:c r="H77" t="str">
+        <x:v>EndUpgradeSelection</x:v>
+      </x:c>
+      <x:c r="I77"/>
+      <x:c r="J77" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K77" t="str">
+        <x:v>结束本次升级选择</x:v>
+      </x:c>
+      <x:c r="L77"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78"/>
+      <x:c r="B78"/>
+      <x:c r="C78"/>
+      <x:c r="D78"/>
+      <x:c r="E78"/>
+      <x:c r="F78"/>
+      <x:c r="G78"/>
+      <x:c r="H78"/>
+      <x:c r="I78"/>
+      <x:c r="J78"/>
+      <x:c r="K78"/>
+      <x:c r="L78"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79"/>
+      <x:c r="B79"/>
+      <x:c r="C79"/>
+      <x:c r="D79"/>
+      <x:c r="E79"/>
+      <x:c r="F79"/>
+      <x:c r="G79"/>
+      <x:c r="H79"/>
+      <x:c r="I79"/>
+      <x:c r="J79"/>
+      <x:c r="K79"/>
+      <x:c r="L79"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80"/>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
+      <x:c r="H80"/>
+      <x:c r="I80"/>
+      <x:c r="J80"/>
+      <x:c r="K80"/>
+      <x:c r="L80"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81"/>
+      <x:c r="B81" t="str">
+        <x:v>EProjectilePattern</x:v>
+      </x:c>
+      <x:c r="C81"/>
+      <x:c r="D81" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81" t="str">
+        <x:v>弹丸投递阵型</x:v>
+      </x:c>
+      <x:c r="H81" t="str">
+        <x:v>Targeted</x:v>
+      </x:c>
+      <x:c r="I81"/>
+      <x:c r="J81" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K81" t="str">
+        <x:v>Targeted</x:v>
+      </x:c>
+      <x:c r="L81"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
+      <x:c r="H82" t="str">
+        <x:v>Fan</x:v>
+      </x:c>
+      <x:c r="I82"/>
+      <x:c r="J82" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K82" t="str">
+        <x:v>Fan</x:v>
+      </x:c>
+      <x:c r="L82"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83"/>
+      <x:c r="G83"/>
+      <x:c r="H83" t="str">
+        <x:v>Radial</x:v>
+      </x:c>
+      <x:c r="I83"/>
+      <x:c r="J83" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K83" t="str">
+        <x:v>Radial</x:v>
+      </x:c>
+      <x:c r="L83"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84"/>
+      <x:c r="B84" t="str">
+        <x:v>ERunEventKind</x:v>
+      </x:c>
+      <x:c r="C84"/>
+      <x:c r="D84" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84" t="str">
+        <x:v>关卡时间事件</x:v>
+      </x:c>
+      <x:c r="H84" t="str">
+        <x:v>EliteSpawn</x:v>
+      </x:c>
+      <x:c r="I84"/>
+      <x:c r="J84" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K84" t="str">
+        <x:v>独立精英出现</x:v>
+      </x:c>
+      <x:c r="L84"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+      <x:c r="G85"/>
+      <x:c r="H85" t="str">
+        <x:v>MapChest</x:v>
+      </x:c>
+      <x:c r="I85"/>
+      <x:c r="J85" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>地图宝箱出现</x:v>
+      </x:c>
+      <x:c r="L85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="B86" t="str">
+        <x:v>ETribulationSignature</x:v>
+      </x:c>
+      <x:c r="D86" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G86" t="str">
+        <x:v>切片职业机制</x:v>
+      </x:c>
+      <x:c r="H86" t="str">
+        <x:v>Guard</x:v>
+      </x:c>
+      <x:c r="J86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K86" t="str">
+        <x:v>有效受击蓄能铁壁</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="H87" t="str">
+        <x:v>Domains</x:v>
+      </x:c>
+      <x:c r="J87" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
+        <x:v>移动留阵重叠引爆</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -1652,49 +1652,40 @@
       </x:c>
       <x:c r="L30" s="101"/>
     </x:row>
-    <x:row r="31" ht="24" customHeight="1">
-      <x:c r="A31" s="101"/>
-      <x:c r="B31" s="101" t="str">
-        <x:v>EPerformanceKind</x:v>
-      </x:c>
-      <x:c r="C31" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D31" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E31" s="101"/>
-      <x:c r="F31" s="101"/>
-      <x:c r="G31" s="101"/>
+    <x:row r="31">
       <x:c r="H31" s="101" t="str">
-        <x:v>SameMonster</x:v>
-      </x:c>
-      <x:c r="I31" s="101"/>
+        <x:v>CastEffect</x:v>
+      </x:c>
       <x:c r="J31" s="101" t="n">
-        <x:v>1</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="101" t="str">
-        <x:v>同种怪物</x:v>
-      </x:c>
-      <x:c r="L31" s="101"/>
+        <x:v>随身施法特效：跟随施法者，不阻塞发射</x:v>
+      </x:c>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="101"/>
-      <x:c r="B32" s="101"/>
-      <x:c r="C32" s="101"/>
-      <x:c r="D32" s="101"/>
+      <x:c r="B32" s="101" t="str">
+        <x:v>EPerformanceKind</x:v>
+      </x:c>
+      <x:c r="C32" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D32" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E32" s="101"/>
       <x:c r="F32" s="101"/>
       <x:c r="G32" s="101"/>
       <x:c r="H32" s="101" t="str">
-        <x:v>MixedMonsters</x:v>
+        <x:v>SameMonster</x:v>
       </x:c>
       <x:c r="I32" s="101"/>
       <x:c r="J32" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K32" s="101" t="str">
-        <x:v>混合怪物</x:v>
+        <x:v>同种怪物</x:v>
       </x:c>
       <x:c r="L32" s="101"/>
     </x:row>
@@ -1707,14 +1698,14 @@
       <x:c r="F33" s="101"/>
       <x:c r="G33" s="101"/>
       <x:c r="H33" s="101" t="str">
-        <x:v>MixedMonstersWithSkills</x:v>
+        <x:v>MixedMonsters</x:v>
       </x:c>
       <x:c r="I33" s="101"/>
       <x:c r="J33" s="101" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K33" s="101" t="str">
-        <x:v>混合怪物与技能</x:v>
+        <x:v>混合怪物</x:v>
       </x:c>
       <x:c r="L33" s="101"/>
     </x:row>
@@ -1727,60 +1718,60 @@
       <x:c r="F34" s="101"/>
       <x:c r="G34" s="101"/>
       <x:c r="H34" s="101" t="str">
-        <x:v>Combat</x:v>
+        <x:v>MixedMonstersWithSkills</x:v>
       </x:c>
       <x:c r="I34" s="101"/>
       <x:c r="J34" s="101" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K34" s="101" t="str">
-        <x:v>完整战斗测试</x:v>
+        <x:v>混合怪物与技能</x:v>
       </x:c>
       <x:c r="L34" s="101"/>
     </x:row>
     <x:row r="35" ht="24" customHeight="1">
       <x:c r="A35" s="101"/>
-      <x:c r="B35" s="101" t="str">
-        <x:v>EAttributeType</x:v>
-      </x:c>
-      <x:c r="C35" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D35" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B35" s="101"/>
+      <x:c r="C35" s="101"/>
+      <x:c r="D35" s="101"/>
       <x:c r="E35" s="101"/>
       <x:c r="F35" s="101"/>
       <x:c r="G35" s="101"/>
       <x:c r="H35" s="101" t="str">
-        <x:v>MaxHealth</x:v>
+        <x:v>Combat</x:v>
       </x:c>
       <x:c r="I35" s="101"/>
       <x:c r="J35" s="101" t="n">
-        <x:v>1</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K35" s="101" t="str">
-        <x:v>最大生命</x:v>
+        <x:v>完整战斗测试</x:v>
       </x:c>
       <x:c r="L35" s="101"/>
     </x:row>
     <x:row r="36" ht="24" customHeight="1">
       <x:c r="A36" s="101"/>
-      <x:c r="B36" s="101"/>
-      <x:c r="C36" s="101"/>
-      <x:c r="D36" s="101"/>
+      <x:c r="B36" s="101" t="str">
+        <x:v>EAttributeType</x:v>
+      </x:c>
+      <x:c r="C36" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D36" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E36" s="101"/>
       <x:c r="F36" s="101"/>
       <x:c r="G36" s="101"/>
       <x:c r="H36" s="101" t="str">
-        <x:v>Attack</x:v>
+        <x:v>MaxHealth</x:v>
       </x:c>
       <x:c r="I36" s="101"/>
       <x:c r="J36" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K36" s="101" t="str">
-        <x:v>攻击</x:v>
+        <x:v>最大生命</x:v>
       </x:c>
       <x:c r="L36" s="101"/>
     </x:row>
@@ -1793,14 +1784,14 @@
       <x:c r="F37" s="101"/>
       <x:c r="G37" s="101"/>
       <x:c r="H37" s="101" t="str">
-        <x:v>Defense</x:v>
+        <x:v>Attack</x:v>
       </x:c>
       <x:c r="I37" s="101"/>
       <x:c r="J37" s="101" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K37" s="101" t="str">
-        <x:v>防御</x:v>
+        <x:v>攻击</x:v>
       </x:c>
       <x:c r="L37" s="101"/>
     </x:row>
@@ -1813,14 +1804,14 @@
       <x:c r="F38" s="101"/>
       <x:c r="G38" s="101"/>
       <x:c r="H38" s="101" t="str">
-        <x:v>MoveSpeed</x:v>
+        <x:v>Defense</x:v>
       </x:c>
       <x:c r="I38" s="101"/>
       <x:c r="J38" s="101" t="n">
-        <x:v>4</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K38" s="101" t="str">
-        <x:v>移动速度</x:v>
+        <x:v>防御</x:v>
       </x:c>
       <x:c r="L38" s="101"/>
     </x:row>
@@ -1833,14 +1824,14 @@
       <x:c r="F39" s="101"/>
       <x:c r="G39" s="101"/>
       <x:c r="H39" s="101" t="str">
-        <x:v>AttackSpeedMultiplier</x:v>
+        <x:v>MoveSpeed</x:v>
       </x:c>
       <x:c r="I39" s="101"/>
       <x:c r="J39" s="101" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K39" s="101" t="str">
-        <x:v>攻速倍率</x:v>
+        <x:v>移动速度</x:v>
       </x:c>
       <x:c r="L39" s="101"/>
     </x:row>
@@ -1853,14 +1844,14 @@
       <x:c r="F40" s="101"/>
       <x:c r="G40" s="101"/>
       <x:c r="H40" s="101" t="str">
-        <x:v>DefenseParameter</x:v>
+        <x:v>AttackSpeedMultiplier</x:v>
       </x:c>
       <x:c r="I40" s="101"/>
       <x:c r="J40" s="101" t="n">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K40" s="101" t="str">
-        <x:v>防御参数</x:v>
+        <x:v>攻速倍率</x:v>
       </x:c>
       <x:c r="L40" s="101"/>
     </x:row>
@@ -1873,14 +1864,14 @@
       <x:c r="F41" s="101"/>
       <x:c r="G41" s="101"/>
       <x:c r="H41" s="101" t="str">
-        <x:v>Hit</x:v>
+        <x:v>DefenseParameter</x:v>
       </x:c>
       <x:c r="I41" s="101"/>
       <x:c r="J41" s="101" t="n">
-        <x:v>7</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K41" s="101" t="str">
-        <x:v>命中值</x:v>
+        <x:v>防御参数</x:v>
       </x:c>
       <x:c r="L41" s="101"/>
     </x:row>
@@ -1893,14 +1884,14 @@
       <x:c r="F42" s="101"/>
       <x:c r="G42" s="101"/>
       <x:c r="H42" s="101" t="str">
-        <x:v>Evasion</x:v>
+        <x:v>Hit</x:v>
       </x:c>
       <x:c r="I42" s="101"/>
       <x:c r="J42" s="101" t="n">
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="K42" s="101" t="str">
-        <x:v>闪避值</x:v>
+        <x:v>命中值</x:v>
       </x:c>
       <x:c r="L42" s="101"/>
     </x:row>
@@ -1913,14 +1904,14 @@
       <x:c r="F43" s="101"/>
       <x:c r="G43" s="101"/>
       <x:c r="H43" s="101" t="str">
-        <x:v>HitParameter</x:v>
+        <x:v>Evasion</x:v>
       </x:c>
       <x:c r="I43" s="101"/>
       <x:c r="J43" s="101" t="n">
-        <x:v>9</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="K43" s="101" t="str">
-        <x:v>命中参数</x:v>
+        <x:v>闪避值</x:v>
       </x:c>
       <x:c r="L43" s="101"/>
     </x:row>
@@ -1933,14 +1924,14 @@
       <x:c r="F44" s="101"/>
       <x:c r="G44" s="101"/>
       <x:c r="H44" s="101" t="str">
-        <x:v>EvasionParameter</x:v>
+        <x:v>HitParameter</x:v>
       </x:c>
       <x:c r="I44" s="101"/>
       <x:c r="J44" s="101" t="n">
-        <x:v>10</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K44" s="101" t="str">
-        <x:v>闪避参数</x:v>
+        <x:v>命中参数</x:v>
       </x:c>
       <x:c r="L44" s="101"/>
     </x:row>
@@ -1953,14 +1944,14 @@
       <x:c r="F45" s="101"/>
       <x:c r="G45" s="101"/>
       <x:c r="H45" s="101" t="str">
-        <x:v>Critical</x:v>
+        <x:v>EvasionParameter</x:v>
       </x:c>
       <x:c r="I45" s="101"/>
       <x:c r="J45" s="101" t="n">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K45" s="101" t="str">
-        <x:v>暴击值</x:v>
+        <x:v>闪避参数</x:v>
       </x:c>
       <x:c r="L45" s="101"/>
     </x:row>
@@ -1973,14 +1964,14 @@
       <x:c r="F46" s="101"/>
       <x:c r="G46" s="101"/>
       <x:c r="H46" s="101" t="str">
-        <x:v>CriticalResistance</x:v>
+        <x:v>Critical</x:v>
       </x:c>
       <x:c r="I46" s="101"/>
       <x:c r="J46" s="101" t="n">
-        <x:v>12</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="K46" s="101" t="str">
-        <x:v>抗暴值</x:v>
+        <x:v>暴击值</x:v>
       </x:c>
       <x:c r="L46" s="101"/>
     </x:row>
@@ -1993,14 +1984,14 @@
       <x:c r="F47" s="101"/>
       <x:c r="G47" s="101"/>
       <x:c r="H47" s="101" t="str">
-        <x:v>CriticalParameter</x:v>
+        <x:v>CriticalResistance</x:v>
       </x:c>
       <x:c r="I47" s="101"/>
       <x:c r="J47" s="101" t="n">
-        <x:v>13</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="K47" s="101" t="str">
-        <x:v>暴击参数</x:v>
+        <x:v>抗暴值</x:v>
       </x:c>
       <x:c r="L47" s="101"/>
     </x:row>
@@ -2013,14 +2004,14 @@
       <x:c r="F48" s="101"/>
       <x:c r="G48" s="101"/>
       <x:c r="H48" s="101" t="str">
-        <x:v>CriticalResistanceParameter</x:v>
+        <x:v>CriticalParameter</x:v>
       </x:c>
       <x:c r="I48" s="101"/>
       <x:c r="J48" s="101" t="n">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K48" s="101" t="str">
-        <x:v>抗暴参数</x:v>
+        <x:v>暴击参数</x:v>
       </x:c>
       <x:c r="L48" s="101"/>
     </x:row>
@@ -2033,106 +2024,106 @@
       <x:c r="F49" s="101"/>
       <x:c r="G49" s="101"/>
       <x:c r="H49" s="101" t="str">
-        <x:v>SkillRangeMultiplier</x:v>
+        <x:v>CriticalResistanceParameter</x:v>
       </x:c>
       <x:c r="I49" s="101"/>
       <x:c r="J49" s="101" t="n">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K49" s="101" t="str">
-        <x:v>技能范围倍率</x:v>
+        <x:v>抗暴参数</x:v>
       </x:c>
       <x:c r="L49" s="101"/>
     </x:row>
     <x:row r="50" ht="24" customHeight="1">
       <x:c r="A50" s="101"/>
-      <x:c r="B50" s="101" t="str">
-        <x:v>EAttributeValueKind</x:v>
-      </x:c>
-      <x:c r="C50" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D50" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B50" s="101"/>
+      <x:c r="C50" s="101"/>
+      <x:c r="D50" s="101"/>
       <x:c r="E50" s="101"/>
       <x:c r="F50" s="101"/>
       <x:c r="G50" s="101"/>
       <x:c r="H50" s="101" t="str">
-        <x:v>Integer</x:v>
+        <x:v>SkillRangeMultiplier</x:v>
       </x:c>
       <x:c r="I50" s="101"/>
       <x:c r="J50" s="101" t="n">
-        <x:v>1</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K50" s="101" t="str">
-        <x:v>整数</x:v>
+        <x:v>技能范围倍率</x:v>
       </x:c>
       <x:c r="L50" s="101"/>
     </x:row>
     <x:row r="51" ht="24" customHeight="1">
       <x:c r="A51" s="101"/>
-      <x:c r="B51" s="101"/>
-      <x:c r="C51" s="101"/>
-      <x:c r="D51" s="101"/>
+      <x:c r="B51" s="101" t="str">
+        <x:v>EAttributeValueKind</x:v>
+      </x:c>
+      <x:c r="C51" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D51" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E51" s="101"/>
       <x:c r="F51" s="101"/>
       <x:c r="G51" s="101"/>
       <x:c r="H51" s="101" t="str">
-        <x:v>Real</x:v>
+        <x:v>Integer</x:v>
       </x:c>
       <x:c r="I51" s="101"/>
       <x:c r="J51" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K51" s="101" t="str">
-        <x:v>实数</x:v>
+        <x:v>整数</x:v>
       </x:c>
       <x:c r="L51" s="101"/>
     </x:row>
     <x:row r="52" ht="24" customHeight="1">
       <x:c r="A52" s="101"/>
-      <x:c r="B52" s="101" t="str">
-        <x:v>ESkillDeliveryType</x:v>
-      </x:c>
-      <x:c r="C52" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D52" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B52" s="101"/>
+      <x:c r="C52" s="101"/>
+      <x:c r="D52" s="101"/>
       <x:c r="E52" s="101"/>
       <x:c r="F52" s="101"/>
       <x:c r="G52" s="101"/>
       <x:c r="H52" s="101" t="str">
-        <x:v>Projectile</x:v>
+        <x:v>Real</x:v>
       </x:c>
       <x:c r="I52" s="101"/>
       <x:c r="J52" s="101" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K52" s="101" t="str">
-        <x:v>直线弹丸</x:v>
+        <x:v>实数</x:v>
       </x:c>
       <x:c r="L52" s="101"/>
     </x:row>
     <x:row r="53" ht="24" customHeight="1">
       <x:c r="A53" s="101"/>
-      <x:c r="B53" s="101"/>
-      <x:c r="C53" s="101"/>
-      <x:c r="D53" s="101"/>
+      <x:c r="B53" s="101" t="str">
+        <x:v>ESkillDeliveryType</x:v>
+      </x:c>
+      <x:c r="C53" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D53" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E53" s="101"/>
       <x:c r="F53" s="101"/>
       <x:c r="G53" s="101"/>
       <x:c r="H53" s="101" t="str">
-        <x:v>Melee</x:v>
+        <x:v>Projectile</x:v>
       </x:c>
       <x:c r="I53" s="101"/>
       <x:c r="J53" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K53" s="101" t="str">
-        <x:v>近战</x:v>
+        <x:v>直线弹丸</x:v>
       </x:c>
       <x:c r="L53" s="101"/>
     </x:row>
@@ -2145,202 +2136,202 @@
       <x:c r="F54" s="101"/>
       <x:c r="G54" s="101"/>
       <x:c r="H54" s="101" t="str">
-        <x:v>TargetArea</x:v>
+        <x:v>Melee</x:v>
       </x:c>
       <x:c r="I54" s="101"/>
-      <x:c r="J54" s="101" t="str">
-        <x:v>3</x:v>
+      <x:c r="J54" s="101" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K54" s="101" t="str">
-        <x:v>目标位置群体释放</x:v>
+        <x:v>近战</x:v>
       </x:c>
       <x:c r="L54" s="101"/>
     </x:row>
     <x:row r="55" ht="24" customHeight="1">
       <x:c r="A55" s="101"/>
-      <x:c r="B55" s="101" t="str">
-        <x:v>ETestHealthPolicy</x:v>
-      </x:c>
-      <x:c r="C55" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D55" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B55" s="101"/>
+      <x:c r="C55" s="101"/>
+      <x:c r="D55" s="101"/>
       <x:c r="E55" s="101"/>
       <x:c r="F55" s="101"/>
       <x:c r="G55" s="101"/>
       <x:c r="H55" s="101" t="str">
-        <x:v>Normal</x:v>
+        <x:v>TargetArea</x:v>
       </x:c>
       <x:c r="I55" s="101"/>
-      <x:c r="J55" s="101" t="n">
-        <x:v>1</x:v>
+      <x:c r="J55" s="101" t="str">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K55" s="101" t="str">
-        <x:v>正常生命</x:v>
+        <x:v>目标位置群体释放</x:v>
       </x:c>
       <x:c r="L55" s="101"/>
     </x:row>
     <x:row r="56" ht="24" customHeight="1">
       <x:c r="A56" s="101"/>
-      <x:c r="B56" s="101"/>
-      <x:c r="C56" s="101"/>
-      <x:c r="D56" s="101"/>
+      <x:c r="B56" s="101" t="str">
+        <x:v>ETestHealthPolicy</x:v>
+      </x:c>
+      <x:c r="C56" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D56" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E56" s="101"/>
       <x:c r="F56" s="101"/>
       <x:c r="G56" s="101"/>
       <x:c r="H56" s="101" t="str">
-        <x:v>RestoreAfterDamage</x:v>
+        <x:v>Normal</x:v>
       </x:c>
       <x:c r="I56" s="101"/>
       <x:c r="J56" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K56" s="101" t="str">
-        <x:v>结算正数扣血后恢复测试玩家生命</x:v>
+        <x:v>正常生命</x:v>
       </x:c>
       <x:c r="L56" s="101"/>
     </x:row>
     <x:row r="57" ht="24" customHeight="1">
       <x:c r="A57" s="101"/>
-      <x:c r="B57" s="101" t="str">
-        <x:v>ETestInputPolicy</x:v>
-      </x:c>
-      <x:c r="C57" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D57" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B57" s="101"/>
+      <x:c r="C57" s="101"/>
+      <x:c r="D57" s="101"/>
       <x:c r="E57" s="101"/>
       <x:c r="F57" s="101"/>
       <x:c r="G57" s="101"/>
       <x:c r="H57" s="101" t="str">
-        <x:v>Manual</x:v>
+        <x:v>RestoreAfterDamage</x:v>
       </x:c>
       <x:c r="I57" s="101"/>
       <x:c r="J57" s="101" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K57" s="101" t="str">
-        <x:v>玩家操作</x:v>
+        <x:v>结算正数扣血后恢复测试玩家生命</x:v>
       </x:c>
       <x:c r="L57" s="101"/>
     </x:row>
     <x:row r="58" ht="24" customHeight="1">
       <x:c r="A58" s="101"/>
-      <x:c r="B58" s="101"/>
-      <x:c r="C58" s="101"/>
-      <x:c r="D58" s="101"/>
+      <x:c r="B58" s="101" t="str">
+        <x:v>ETestInputPolicy</x:v>
+      </x:c>
+      <x:c r="C58" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D58" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E58" s="101"/>
       <x:c r="F58" s="101"/>
       <x:c r="G58" s="101"/>
       <x:c r="H58" s="101" t="str">
-        <x:v>Stationary</x:v>
+        <x:v>Manual</x:v>
       </x:c>
       <x:c r="I58" s="101"/>
       <x:c r="J58" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K58" s="101" t="str">
-        <x:v>玩家静止</x:v>
+        <x:v>玩家操作</x:v>
       </x:c>
       <x:c r="L58" s="101"/>
     </x:row>
     <x:row r="59" ht="24" customHeight="1">
       <x:c r="A59" s="101"/>
-      <x:c r="B59" s="101" t="str">
-        <x:v>EMovementType</x:v>
-      </x:c>
-      <x:c r="C59" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D59" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B59" s="101"/>
+      <x:c r="C59" s="101"/>
+      <x:c r="D59" s="101"/>
       <x:c r="E59" s="101"/>
-      <x:c r="F59" s="101" t="str">
-        <x:v>单位移动分类</x:v>
-      </x:c>
+      <x:c r="F59" s="101"/>
       <x:c r="G59" s="101"/>
       <x:c r="H59" s="101" t="str">
-        <x:v>Ground</x:v>
+        <x:v>Stationary</x:v>
       </x:c>
       <x:c r="I59" s="101"/>
-      <x:c r="J59" s="101" t="str">
-        <x:v>1</x:v>
+      <x:c r="J59" s="101" t="n">
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K59" s="101" t="str">
-        <x:v>地面</x:v>
+        <x:v>玩家静止</x:v>
       </x:c>
       <x:c r="L59" s="101"/>
     </x:row>
     <x:row r="60" ht="24" customHeight="1">
       <x:c r="A60" s="101"/>
-      <x:c r="B60" s="101"/>
-      <x:c r="C60" s="101"/>
-      <x:c r="D60" s="101"/>
+      <x:c r="B60" s="101" t="str">
+        <x:v>EMovementType</x:v>
+      </x:c>
+      <x:c r="C60" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D60" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E60" s="101"/>
-      <x:c r="F60" s="101"/>
+      <x:c r="F60" s="101" t="str">
+        <x:v>单位移动分类</x:v>
+      </x:c>
       <x:c r="G60" s="101"/>
       <x:c r="H60" s="101" t="str">
-        <x:v>Flying</x:v>
+        <x:v>Ground</x:v>
       </x:c>
       <x:c r="I60" s="101"/>
       <x:c r="J60" s="101" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K60" s="101" t="str">
-        <x:v>飞行</x:v>
+        <x:v>地面</x:v>
       </x:c>
       <x:c r="L60" s="101"/>
     </x:row>
     <x:row r="61" ht="24" customHeight="1">
       <x:c r="A61" s="101"/>
-      <x:c r="B61" s="101" t="str">
-        <x:v>EUpgradeOptionType</x:v>
-      </x:c>
-      <x:c r="C61" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D61" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B61" s="101"/>
+      <x:c r="C61" s="101"/>
+      <x:c r="D61" s="101"/>
       <x:c r="E61" s="101"/>
-      <x:c r="F61" s="101" t="str">
-        <x:v>局内升级选项类型</x:v>
-      </x:c>
+      <x:c r="F61" s="101"/>
       <x:c r="G61" s="101"/>
       <x:c r="H61" s="101" t="str">
-        <x:v>SkillUnlock</x:v>
+        <x:v>Flying</x:v>
       </x:c>
       <x:c r="I61" s="101"/>
       <x:c r="J61" s="101" t="str">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K61" s="101" t="str">
-        <x:v>解锁技能</x:v>
+        <x:v>飞行</x:v>
       </x:c>
       <x:c r="L61" s="101"/>
     </x:row>
     <x:row r="62" ht="24" customHeight="1">
       <x:c r="A62" s="101"/>
-      <x:c r="B62" s="101"/>
-      <x:c r="C62" s="101"/>
-      <x:c r="D62" s="101"/>
+      <x:c r="B62" s="101" t="str">
+        <x:v>EUpgradeOptionType</x:v>
+      </x:c>
+      <x:c r="C62" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D62" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E62" s="101"/>
-      <x:c r="F62" s="101"/>
+      <x:c r="F62" s="101" t="str">
+        <x:v>局内升级选项类型</x:v>
+      </x:c>
       <x:c r="G62" s="101"/>
       <x:c r="H62" s="101" t="str">
-        <x:v>Attribute</x:v>
+        <x:v>SkillUnlock</x:v>
       </x:c>
       <x:c r="I62" s="101"/>
       <x:c r="J62" s="101" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K62" s="101" t="str">
-        <x:v>属性强化</x:v>
+        <x:v>解锁技能</x:v>
       </x:c>
       <x:c r="L62" s="101"/>
     </x:row>
@@ -2353,14 +2344,14 @@
       <x:c r="F63" s="101"/>
       <x:c r="G63" s="101"/>
       <x:c r="H63" s="101" t="str">
-        <x:v>Heal</x:v>
+        <x:v>Attribute</x:v>
       </x:c>
       <x:c r="I63" s="101"/>
       <x:c r="J63" s="101" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K63" s="101" t="str">
-        <x:v>立即恢复</x:v>
+        <x:v>属性强化</x:v>
       </x:c>
       <x:c r="L63" s="101"/>
     </x:row>
@@ -2373,14 +2364,14 @@
       <x:c r="F64" s="101"/>
       <x:c r="G64" s="101"/>
       <x:c r="H64" s="101" t="str">
-        <x:v>RunWeapon</x:v>
+        <x:v>Heal</x:v>
       </x:c>
       <x:c r="I64" s="101"/>
-      <x:c r="J64" s="101" t="n">
-        <x:v>4</x:v>
+      <x:c r="J64" s="101" t="str">
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K64" s="101" t="str">
-        <x:v>获得武器或升星</x:v>
+        <x:v>立即恢复</x:v>
       </x:c>
       <x:c r="L64" s="101"/>
     </x:row>
@@ -2393,62 +2384,62 @@
       <x:c r="F65" s="101"/>
       <x:c r="G65" s="101"/>
       <x:c r="H65" s="101" t="str">
-        <x:v>RunPassive</x:v>
+        <x:v>RunWeapon</x:v>
       </x:c>
       <x:c r="I65" s="101"/>
       <x:c r="J65" s="101" t="n">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="K65" s="101" t="str">
-        <x:v>获得被动或升级</x:v>
+        <x:v>获得武器或升星</x:v>
       </x:c>
       <x:c r="L65" s="101"/>
     </x:row>
     <x:row r="66" ht="24" customHeight="1">
       <x:c r="A66" s="101"/>
-      <x:c r="B66" s="101" t="str">
-        <x:v>EAttributeModifyOperation</x:v>
-      </x:c>
-      <x:c r="C66" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D66" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B66" s="101"/>
+      <x:c r="C66" s="101"/>
+      <x:c r="D66" s="101"/>
       <x:c r="E66" s="101"/>
-      <x:c r="F66" s="101" t="str">
-        <x:v>局内属性修改操作</x:v>
-      </x:c>
+      <x:c r="F66" s="101"/>
       <x:c r="G66" s="101"/>
       <x:c r="H66" s="101" t="str">
-        <x:v>Add</x:v>
+        <x:v>RunPassive</x:v>
       </x:c>
       <x:c r="I66" s="101"/>
-      <x:c r="J66" s="101" t="str">
-        <x:v>1</x:v>
+      <x:c r="J66" s="101" t="n">
+        <x:v>5</x:v>
       </x:c>
       <x:c r="K66" s="101" t="str">
-        <x:v>固定值相加</x:v>
+        <x:v>获得被动或升级</x:v>
       </x:c>
       <x:c r="L66" s="101"/>
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
       <x:c r="A67" s="101"/>
-      <x:c r="B67" s="101"/>
-      <x:c r="C67" s="101"/>
-      <x:c r="D67" s="101"/>
+      <x:c r="B67" s="101" t="str">
+        <x:v>EAttributeModifyOperation</x:v>
+      </x:c>
+      <x:c r="C67" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D67" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E67" s="101"/>
-      <x:c r="F67" s="101"/>
+      <x:c r="F67" s="101" t="str">
+        <x:v>局内属性修改操作</x:v>
+      </x:c>
       <x:c r="G67" s="101"/>
       <x:c r="H67" s="101" t="str">
-        <x:v>AddPercent</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="I67" s="101"/>
       <x:c r="J67" s="101" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K67" s="101" t="str">
-        <x:v>基础值百分比相加</x:v>
+        <x:v>固定值相加</x:v>
       </x:c>
       <x:c r="L67" s="101"/>
     </x:row>
@@ -2461,62 +2452,62 @@
       <x:c r="F68" s="101"/>
       <x:c r="G68" s="101"/>
       <x:c r="H68" s="101" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>AddPercent</x:v>
       </x:c>
       <x:c r="I68" s="101"/>
       <x:c r="J68" s="101" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K68" s="101" t="str">
-        <x:v>最终值相乘</x:v>
+        <x:v>基础值百分比相加</x:v>
       </x:c>
       <x:c r="L68" s="101"/>
     </x:row>
     <x:row r="69" ht="24" customHeight="1">
       <x:c r="A69" s="101"/>
-      <x:c r="B69" s="101" t="str">
-        <x:v>ERunResultType</x:v>
-      </x:c>
-      <x:c r="C69" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D69" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B69" s="101"/>
+      <x:c r="C69" s="101"/>
+      <x:c r="D69" s="101"/>
       <x:c r="E69" s="101"/>
-      <x:c r="F69" s="101" t="str">
-        <x:v>单局结算结果</x:v>
-      </x:c>
+      <x:c r="F69" s="101"/>
       <x:c r="G69" s="101"/>
       <x:c r="H69" s="101" t="str">
-        <x:v>Victory</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="I69" s="101"/>
       <x:c r="J69" s="101" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K69" s="101" t="str">
-        <x:v>胜利</x:v>
+        <x:v>最终值相乘</x:v>
       </x:c>
       <x:c r="L69" s="101"/>
     </x:row>
     <x:row r="70" ht="24" customHeight="1">
       <x:c r="A70" s="101"/>
-      <x:c r="B70" s="101"/>
-      <x:c r="C70" s="101"/>
-      <x:c r="D70" s="101"/>
+      <x:c r="B70" s="101" t="str">
+        <x:v>ERunResultType</x:v>
+      </x:c>
+      <x:c r="C70" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D70" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E70" s="101"/>
-      <x:c r="F70" s="101"/>
+      <x:c r="F70" s="101" t="str">
+        <x:v>单局结算结果</x:v>
+      </x:c>
       <x:c r="G70" s="101"/>
       <x:c r="H70" s="101" t="str">
-        <x:v>Defeat</x:v>
+        <x:v>Victory</x:v>
       </x:c>
       <x:c r="I70" s="101"/>
       <x:c r="J70" s="101" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K70" s="101" t="str">
-        <x:v>失败</x:v>
+        <x:v>胜利</x:v>
       </x:c>
       <x:c r="L70" s="101"/>
     </x:row>
@@ -2528,31 +2519,27 @@
       <x:c r="E71" s="101"/>
       <x:c r="F71" s="101"/>
       <x:c r="G71" s="101"/>
-      <x:c r="H71" s="101"/>
+      <x:c r="H71" s="101" t="str">
+        <x:v>Defeat</x:v>
+      </x:c>
       <x:c r="I71" s="101"/>
-      <x:c r="J71" s="101"/>
-      <x:c r="K71" s="101"/>
+      <x:c r="J71" s="101" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K71" s="101" t="str">
+        <x:v>失败</x:v>
+      </x:c>
       <x:c r="L71" s="101"/>
     </x:row>
     <x:row r="72" ht="24" customHeight="1">
       <x:c r="A72" s="101"/>
-      <x:c r="B72" s="101" t="str">
-        <x:v>EUnitCollisionShape</x:v>
-      </x:c>
-      <x:c r="C72" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D72" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B72" s="101"/>
+      <x:c r="C72" s="101"/>
+      <x:c r="D72" s="101"/>
       <x:c r="E72" s="101"/>
-      <x:c r="F72" s="101" t="str">
-        <x:v>单位统一碰撞形状</x:v>
-      </x:c>
+      <x:c r="F72" s="101"/>
       <x:c r="G72" s="101"/>
-      <x:c r="H72" s="101" t="str">
-        <x:v>VerticalCapsule</x:v>
-      </x:c>
+      <x:c r="H72" s="101"/>
       <x:c r="I72" s="101"/>
       <x:c r="J72" s="101"/>
       <x:c r="K72" s="101"/>
@@ -2561,7 +2548,7 @@
     <x:row r="73" ht="24" customHeight="1">
       <x:c r="A73" s="101"/>
       <x:c r="B73" s="101" t="str">
-        <x:v>EResourcePackage</x:v>
+        <x:v>EUnitCollisionShape</x:v>
       </x:c>
       <x:c r="C73" s="102" t="b">
         <x:v>0</x:v>
@@ -2571,86 +2558,90 @@
       </x:c>
       <x:c r="E73" s="101"/>
       <x:c r="F73" s="101" t="str">
-        <x:v>资源包归属</x:v>
+        <x:v>单位统一碰撞形状</x:v>
       </x:c>
       <x:c r="G73" s="101"/>
       <x:c r="H73" s="101" t="str">
-        <x:v>Raw</x:v>
+        <x:v>VerticalCapsule</x:v>
       </x:c>
       <x:c r="I73" s="101"/>
-      <x:c r="J73" s="101" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K73" s="101" t="str">
-        <x:v>原始字节包</x:v>
-      </x:c>
+      <x:c r="J73" s="101"/>
+      <x:c r="K73" s="101"/>
       <x:c r="L73" s="101"/>
     </x:row>
     <x:row r="74" ht="24" customHeight="1">
       <x:c r="A74" s="101"/>
-      <x:c r="B74" s="101"/>
-      <x:c r="C74" s="101"/>
-      <x:c r="D74" s="101"/>
+      <x:c r="B74" s="101" t="str">
+        <x:v>EResourcePackage</x:v>
+      </x:c>
+      <x:c r="C74" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D74" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E74" s="101"/>
-      <x:c r="F74" s="101"/>
+      <x:c r="F74" s="101" t="str">
+        <x:v>资源包归属</x:v>
+      </x:c>
       <x:c r="G74" s="101"/>
       <x:c r="H74" s="101" t="str">
-        <x:v>GameAsset</x:v>
+        <x:v>Raw</x:v>
       </x:c>
       <x:c r="I74" s="101"/>
       <x:c r="J74" s="101" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K74" s="101" t="str">
+        <x:v>原始字节包</x:v>
+      </x:c>
+      <x:c r="L74" s="101"/>
+    </x:row>
+    <x:row r="75" ht="24" customHeight="1">
+      <x:c r="A75" s="101"/>
+      <x:c r="B75" s="101"/>
+      <x:c r="C75" s="101"/>
+      <x:c r="D75" s="101"/>
+      <x:c r="E75" s="101"/>
+      <x:c r="F75" s="101"/>
+      <x:c r="G75" s="101"/>
+      <x:c r="H75" s="101" t="str">
+        <x:v>GameAsset</x:v>
+      </x:c>
+      <x:c r="I75" s="101"/>
+      <x:c r="J75" s="101" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K74" s="101" t="str">
+      <x:c r="K75" s="101" t="str">
         <x:v>Unity资产包</x:v>
       </x:c>
-      <x:c r="L74" s="101"/>
-    </x:row>
-    <x:row r="75" ht="24" customHeight="1">
-      <x:c r="A75"/>
-      <x:c r="B75" t="str">
-        <x:v>EUpgradeExhaustionPolicy</x:v>
-      </x:c>
-      <x:c r="C75" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D75" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E75"/>
-      <x:c r="F75" t="str">
-        <x:v>升级候选耗尽策略</x:v>
-      </x:c>
-      <x:c r="G75"/>
-      <x:c r="H75" t="str">
-        <x:v>ReduceOfferCount</x:v>
-      </x:c>
-      <x:c r="I75"/>
-      <x:c r="J75" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K75" t="str">
-        <x:v>按剩余合法候选降量展示</x:v>
-      </x:c>
-      <x:c r="L75"/>
+      <x:c r="L75" s="101"/>
     </x:row>
     <x:row r="76" ht="24" customHeight="1">
       <x:c r="A76"/>
-      <x:c r="B76"/>
-      <x:c r="C76"/>
-      <x:c r="D76"/>
+      <x:c r="B76" t="str">
+        <x:v>EUpgradeExhaustionPolicy</x:v>
+      </x:c>
+      <x:c r="C76" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D76" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E76"/>
-      <x:c r="F76"/>
+      <x:c r="F76" t="str">
+        <x:v>升级候选耗尽策略</x:v>
+      </x:c>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>FallbackPool</x:v>
+        <x:v>ReduceOfferCount</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>切换后备池重新筛选</x:v>
+        <x:v>按剩余合法候选降量展示</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
@@ -2663,18 +2654,18 @@
       <x:c r="F77"/>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>EndUpgradeSelection</x:v>
+        <x:v>FallbackPool</x:v>
       </x:c>
       <x:c r="I77"/>
       <x:c r="J77" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>结束本次升级选择</x:v>
+        <x:v>切换后备池重新筛选</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
-    <x:row r="78">
+    <x:row r="78" ht="24" customHeight="1">
       <x:c r="A78"/>
       <x:c r="B78"/>
       <x:c r="C78"/>
@@ -2682,10 +2673,16 @@
       <x:c r="E78"/>
       <x:c r="F78"/>
       <x:c r="G78"/>
-      <x:c r="H78"/>
+      <x:c r="H78" t="str">
+        <x:v>EndUpgradeSelection</x:v>
+      </x:c>
       <x:c r="I78"/>
-      <x:c r="J78"/>
-      <x:c r="K78"/>
+      <x:c r="J78" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K78" t="str">
+        <x:v>结束本次升级选择</x:v>
+      </x:c>
       <x:c r="L78"/>
     </x:row>
     <x:row r="79">
@@ -2718,47 +2715,41 @@
     </x:row>
     <x:row r="81">
       <x:c r="A81"/>
-      <x:c r="B81" t="str">
-        <x:v>EProjectilePattern</x:v>
-      </x:c>
+      <x:c r="B81"/>
       <x:c r="C81"/>
-      <x:c r="D81" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D81"/>
       <x:c r="E81"/>
       <x:c r="F81"/>
-      <x:c r="G81" t="str">
-        <x:v>弹丸投递阵型</x:v>
-      </x:c>
-      <x:c r="H81" t="str">
-        <x:v>Targeted</x:v>
-      </x:c>
+      <x:c r="G81"/>
+      <x:c r="H81"/>
       <x:c r="I81"/>
-      <x:c r="J81" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K81" t="str">
-        <x:v>Targeted</x:v>
-      </x:c>
+      <x:c r="J81"/>
+      <x:c r="K81"/>
       <x:c r="L81"/>
     </x:row>
     <x:row r="82">
       <x:c r="A82"/>
-      <x:c r="B82"/>
+      <x:c r="B82" t="str">
+        <x:v>EProjectilePattern</x:v>
+      </x:c>
       <x:c r="C82"/>
-      <x:c r="D82"/>
+      <x:c r="D82" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E82"/>
       <x:c r="F82"/>
-      <x:c r="G82"/>
+      <x:c r="G82" t="str">
+        <x:v>弹丸投递阵型</x:v>
+      </x:c>
       <x:c r="H82" t="str">
-        <x:v>Fan</x:v>
+        <x:v>Targeted</x:v>
       </x:c>
       <x:c r="I82"/>
       <x:c r="J82" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K82" t="str">
-        <x:v>Fan</x:v>
+        <x:v>Targeted</x:v>
       </x:c>
       <x:c r="L82"/>
     </x:row>
@@ -2771,91 +2762,111 @@
       <x:c r="F83"/>
       <x:c r="G83"/>
       <x:c r="H83" t="str">
-        <x:v>Radial</x:v>
+        <x:v>Fan</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>Radial</x:v>
+        <x:v>Fan</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
     <x:row r="84">
       <x:c r="A84"/>
-      <x:c r="B84" t="str">
-        <x:v>ERunEventKind</x:v>
-      </x:c>
+      <x:c r="B84"/>
       <x:c r="C84"/>
-      <x:c r="D84" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D84"/>
       <x:c r="E84"/>
       <x:c r="F84"/>
-      <x:c r="G84" t="str">
-        <x:v>关卡时间事件</x:v>
-      </x:c>
+      <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>EliteSpawn</x:v>
+        <x:v>Radial</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>独立精英出现</x:v>
+        <x:v>Radial</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85"/>
-      <x:c r="B85"/>
+      <x:c r="B85" t="str">
+        <x:v>ERunEventKind</x:v>
+      </x:c>
       <x:c r="C85"/>
-      <x:c r="D85"/>
+      <x:c r="D85" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E85"/>
       <x:c r="F85"/>
-      <x:c r="G85"/>
+      <x:c r="G85" t="str">
+        <x:v>关卡时间事件</x:v>
+      </x:c>
       <x:c r="H85" t="str">
-        <x:v>MapChest</x:v>
+        <x:v>EliteSpawn</x:v>
       </x:c>
       <x:c r="I85"/>
       <x:c r="J85" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K85" t="str">
+        <x:v>独立精英出现</x:v>
+      </x:c>
+      <x:c r="L85"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+      <x:c r="G86"/>
+      <x:c r="H86" t="str">
+        <x:v>MapChest</x:v>
+      </x:c>
+      <x:c r="I86"/>
+      <x:c r="J86" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K85" t="str">
+      <x:c r="K86" t="str">
         <x:v>地图宝箱出现</x:v>
       </x:c>
-      <x:c r="L85"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="B86" t="str">
+      <x:c r="L86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="B87" t="str">
         <x:v>ETribulationSignature</x:v>
       </x:c>
-      <x:c r="D86" s="1" t="b">
+      <x:c r="D87" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G86" t="str">
+      <x:c r="G87" t="str">
         <x:v>切片职业机制</x:v>
       </x:c>
-      <x:c r="H86" t="str">
+      <x:c r="H87" t="str">
         <x:v>Guard</x:v>
       </x:c>
-      <x:c r="J86" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K86" t="str">
+      <x:c r="J87" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K87" t="str">
         <x:v>有效受击蓄能铁壁</x:v>
       </x:c>
     </x:row>
-    <x:row r="87">
-      <x:c r="H87" t="str">
+    <x:row r="88">
+      <x:c r="H88" t="str">
         <x:v>Domains</x:v>
       </x:c>
-      <x:c r="J87" t="n">
+      <x:c r="J88" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K87" t="str">
+      <x:c r="K88" t="str">
         <x:v>移动留阵重叠引爆</x:v>
       </x:c>
     </x:row>

--- a/Config/Datas/__enums__.xlsx
+++ b/Config/Datas/__enums__.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="R621839dc00424df8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enums" sheetId="1" r:id="Rdc08a6f297ce4009"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1653,15 +1653,24 @@
       <x:c r="L30" s="101"/>
     </x:row>
     <x:row r="31">
+      <x:c r="A31"/>
+      <x:c r="B31"/>
+      <x:c r="C31"/>
+      <x:c r="D31"/>
+      <x:c r="E31"/>
+      <x:c r="F31"/>
+      <x:c r="G31"/>
       <x:c r="H31" s="101" t="str">
         <x:v>CastEffect</x:v>
       </x:c>
+      <x:c r="I31"/>
       <x:c r="J31" s="101" t="n">
         <x:v>14</x:v>
       </x:c>
       <x:c r="K31" s="101" t="str">
         <x:v>随身施法特效：跟随施法者，不阻塞发射</x:v>
       </x:c>
+      <x:c r="L31"/>
     </x:row>
     <x:row r="32" ht="24" customHeight="1">
       <x:c r="A32" s="101"/>
@@ -2417,49 +2426,49 @@
     </x:row>
     <x:row r="67" ht="24" customHeight="1">
       <x:c r="A67" s="101"/>
-      <x:c r="B67" s="101" t="str">
-        <x:v>EAttributeModifyOperation</x:v>
-      </x:c>
-      <x:c r="C67" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D67" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B67" s="101"/>
+      <x:c r="C67" s="101"/>
+      <x:c r="D67" s="101"/>
       <x:c r="E67" s="101"/>
-      <x:c r="F67" s="101" t="str">
-        <x:v>局内属性修改操作</x:v>
-      </x:c>
+      <x:c r="F67" s="101"/>
       <x:c r="G67" s="101"/>
       <x:c r="H67" s="101" t="str">
-        <x:v>Add</x:v>
+        <x:v>MechanismModifier</x:v>
       </x:c>
       <x:c r="I67" s="101"/>
-      <x:c r="J67" s="101" t="str">
-        <x:v>1</x:v>
+      <x:c r="J67" s="101" t="n">
+        <x:v>6</x:v>
       </x:c>
       <x:c r="K67" s="101" t="str">
-        <x:v>固定值相加</x:v>
+        <x:v>单级职业机制修饰</x:v>
       </x:c>
       <x:c r="L67" s="101"/>
     </x:row>
     <x:row r="68" ht="24" customHeight="1">
       <x:c r="A68" s="101"/>
-      <x:c r="B68" s="101"/>
-      <x:c r="C68" s="101"/>
-      <x:c r="D68" s="101"/>
+      <x:c r="B68" s="101" t="str">
+        <x:v>EAttributeModifyOperation</x:v>
+      </x:c>
+      <x:c r="C68" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D68" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E68" s="101"/>
-      <x:c r="F68" s="101"/>
+      <x:c r="F68" s="101" t="str">
+        <x:v>局内属性修改操作</x:v>
+      </x:c>
       <x:c r="G68" s="101"/>
       <x:c r="H68" s="101" t="str">
-        <x:v>AddPercent</x:v>
+        <x:v>Add</x:v>
       </x:c>
       <x:c r="I68" s="101"/>
       <x:c r="J68" s="101" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K68" s="101" t="str">
-        <x:v>基础值百分比相加</x:v>
+        <x:v>固定值相加</x:v>
       </x:c>
       <x:c r="L68" s="101"/>
     </x:row>
@@ -2472,62 +2481,62 @@
       <x:c r="F69" s="101"/>
       <x:c r="G69" s="101"/>
       <x:c r="H69" s="101" t="str">
-        <x:v>Multiply</x:v>
+        <x:v>AddPercent</x:v>
       </x:c>
       <x:c r="I69" s="101"/>
       <x:c r="J69" s="101" t="str">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K69" s="101" t="str">
-        <x:v>最终值相乘</x:v>
+        <x:v>基础值百分比相加</x:v>
       </x:c>
       <x:c r="L69" s="101"/>
     </x:row>
     <x:row r="70" ht="24" customHeight="1">
       <x:c r="A70" s="101"/>
-      <x:c r="B70" s="101" t="str">
-        <x:v>ERunResultType</x:v>
-      </x:c>
-      <x:c r="C70" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D70" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B70" s="101"/>
+      <x:c r="C70" s="101"/>
+      <x:c r="D70" s="101"/>
       <x:c r="E70" s="101"/>
-      <x:c r="F70" s="101" t="str">
-        <x:v>单局结算结果</x:v>
-      </x:c>
+      <x:c r="F70" s="101"/>
       <x:c r="G70" s="101"/>
       <x:c r="H70" s="101" t="str">
-        <x:v>Victory</x:v>
+        <x:v>Multiply</x:v>
       </x:c>
       <x:c r="I70" s="101"/>
       <x:c r="J70" s="101" t="str">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K70" s="101" t="str">
-        <x:v>胜利</x:v>
+        <x:v>最终值相乘</x:v>
       </x:c>
       <x:c r="L70" s="101"/>
     </x:row>
     <x:row r="71" ht="24" customHeight="1">
       <x:c r="A71" s="101"/>
-      <x:c r="B71" s="101"/>
-      <x:c r="C71" s="101"/>
-      <x:c r="D71" s="101"/>
+      <x:c r="B71" s="101" t="str">
+        <x:v>ERunResultType</x:v>
+      </x:c>
+      <x:c r="C71" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D71" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E71" s="101"/>
-      <x:c r="F71" s="101"/>
+      <x:c r="F71" s="101" t="str">
+        <x:v>单局结算结果</x:v>
+      </x:c>
       <x:c r="G71" s="101"/>
       <x:c r="H71" s="101" t="str">
-        <x:v>Defeat</x:v>
+        <x:v>Victory</x:v>
       </x:c>
       <x:c r="I71" s="101"/>
       <x:c r="J71" s="101" t="str">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K71" s="101" t="str">
-        <x:v>失败</x:v>
+        <x:v>胜利</x:v>
       </x:c>
       <x:c r="L71" s="101"/>
     </x:row>
@@ -2539,31 +2548,27 @@
       <x:c r="E72" s="101"/>
       <x:c r="F72" s="101"/>
       <x:c r="G72" s="101"/>
-      <x:c r="H72" s="101"/>
+      <x:c r="H72" s="101" t="str">
+        <x:v>Defeat</x:v>
+      </x:c>
       <x:c r="I72" s="101"/>
-      <x:c r="J72" s="101"/>
-      <x:c r="K72" s="101"/>
+      <x:c r="J72" s="101" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K72" s="101" t="str">
+        <x:v>失败</x:v>
+      </x:c>
       <x:c r="L72" s="101"/>
     </x:row>
     <x:row r="73" ht="24" customHeight="1">
       <x:c r="A73" s="101"/>
-      <x:c r="B73" s="101" t="str">
-        <x:v>EUnitCollisionShape</x:v>
-      </x:c>
-      <x:c r="C73" s="102" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D73" s="102" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B73" s="101"/>
+      <x:c r="C73" s="101"/>
+      <x:c r="D73" s="101"/>
       <x:c r="E73" s="101"/>
-      <x:c r="F73" s="101" t="str">
-        <x:v>单位统一碰撞形状</x:v>
-      </x:c>
+      <x:c r="F73" s="101"/>
       <x:c r="G73" s="101"/>
-      <x:c r="H73" s="101" t="str">
-        <x:v>VerticalCapsule</x:v>
-      </x:c>
+      <x:c r="H73" s="101"/>
       <x:c r="I73" s="101"/>
       <x:c r="J73" s="101"/>
       <x:c r="K73" s="101"/>
@@ -2572,7 +2577,7 @@
     <x:row r="74" ht="24" customHeight="1">
       <x:c r="A74" s="101"/>
       <x:c r="B74" s="101" t="str">
-        <x:v>EResourcePackage</x:v>
+        <x:v>EUnitCollisionShape</x:v>
       </x:c>
       <x:c r="C74" s="102" t="b">
         <x:v>0</x:v>
@@ -2582,86 +2587,90 @@
       </x:c>
       <x:c r="E74" s="101"/>
       <x:c r="F74" s="101" t="str">
-        <x:v>资源包归属</x:v>
+        <x:v>单位统一碰撞形状</x:v>
       </x:c>
       <x:c r="G74" s="101"/>
       <x:c r="H74" s="101" t="str">
-        <x:v>Raw</x:v>
+        <x:v>VerticalCapsule</x:v>
       </x:c>
       <x:c r="I74" s="101"/>
-      <x:c r="J74" s="101" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K74" s="101" t="str">
-        <x:v>原始字节包</x:v>
-      </x:c>
+      <x:c r="J74" s="101"/>
+      <x:c r="K74" s="101"/>
       <x:c r="L74" s="101"/>
     </x:row>
     <x:row r="75" ht="24" customHeight="1">
       <x:c r="A75" s="101"/>
-      <x:c r="B75" s="101"/>
-      <x:c r="C75" s="101"/>
-      <x:c r="D75" s="101"/>
+      <x:c r="B75" s="101" t="str">
+        <x:v>EResourcePackage</x:v>
+      </x:c>
+      <x:c r="C75" s="102" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D75" s="102" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E75" s="101"/>
-      <x:c r="F75" s="101"/>
+      <x:c r="F75" s="101" t="str">
+        <x:v>资源包归属</x:v>
+      </x:c>
       <x:c r="G75" s="101"/>
       <x:c r="H75" s="101" t="str">
-        <x:v>GameAsset</x:v>
+        <x:v>Raw</x:v>
       </x:c>
       <x:c r="I75" s="101"/>
       <x:c r="J75" s="101" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K75" s="101" t="str">
-        <x:v>Unity资产包</x:v>
+        <x:v>原始字节包</x:v>
       </x:c>
       <x:c r="L75" s="101"/>
     </x:row>
     <x:row r="76" ht="24" customHeight="1">
       <x:c r="A76"/>
-      <x:c r="B76" t="str">
-        <x:v>EUpgradeExhaustionPolicy</x:v>
-      </x:c>
-      <x:c r="C76" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D76" s="1" t="b">
-        <x:v>1</x:v>
-      </x:c>
+      <x:c r="B76"/>
+      <x:c r="C76"/>
+      <x:c r="D76"/>
       <x:c r="E76"/>
-      <x:c r="F76" t="str">
-        <x:v>升级候选耗尽策略</x:v>
-      </x:c>
+      <x:c r="F76"/>
       <x:c r="G76"/>
       <x:c r="H76" t="str">
-        <x:v>ReduceOfferCount</x:v>
+        <x:v>GameAsset</x:v>
       </x:c>
       <x:c r="I76"/>
       <x:c r="J76" t="n">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K76" t="str">
-        <x:v>按剩余合法候选降量展示</x:v>
+        <x:v>Unity资产包</x:v>
       </x:c>
       <x:c r="L76"/>
     </x:row>
     <x:row r="77" ht="24" customHeight="1">
       <x:c r="A77"/>
-      <x:c r="B77"/>
-      <x:c r="C77"/>
-      <x:c r="D77"/>
+      <x:c r="B77" t="str">
+        <x:v>EUpgradeExhaustionPolicy</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="b">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="E77"/>
-      <x:c r="F77"/>
+      <x:c r="F77" t="str">
+        <x:v>升级候选耗尽策略</x:v>
+      </x:c>
       <x:c r="G77"/>
       <x:c r="H77" t="str">
-        <x:v>FallbackPool</x:v>
+        <x:v>ReduceOfferCount</x:v>
       </x:c>
       <x:c r="I77"/>
       <x:c r="J77" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K77" t="str">
-        <x:v>切换后备池重新筛选</x:v>
+        <x:v>按剩余合法候选降量展示</x:v>
       </x:c>
       <x:c r="L77"/>
     </x:row>
@@ -2674,14 +2683,14 @@
       <x:c r="F78"/>
       <x:c r="G78"/>
       <x:c r="H78" t="str">
-        <x:v>EndUpgradeSelection</x:v>
+        <x:v>FallbackPool</x:v>
       </x:c>
       <x:c r="I78"/>
       <x:c r="J78" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K78" t="str">
-        <x:v>结束本次升级选择</x:v>
+        <x:v>切换后备池重新筛选</x:v>
       </x:c>
       <x:c r="L78"/>
     </x:row>
@@ -2693,10 +2702,16 @@
       <x:c r="E79"/>
       <x:c r="F79"/>
       <x:c r="G79"/>
-      <x:c r="H79"/>
+      <x:c r="H79" t="str">
+        <x:v>EndUpgradeSelection</x:v>
+      </x:c>
       <x:c r="I79"/>
-      <x:c r="J79"/>
-      <x:c r="K79"/>
+      <x:c r="J79" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K79" t="str">
+        <x:v>结束本次升级选择</x:v>
+      </x:c>
       <x:c r="L79"/>
     </x:row>
     <x:row r="80">
@@ -2729,47 +2744,41 @@
     </x:row>
     <x:row r="82">
       <x:c r="A82"/>
-      <x:c r="B82" t="str">
-        <x:v>EProjectilePattern</x:v>
-      </x:c>
+      <x:c r="B82"/>
       <x:c r="C82"/>
-      <x:c r="D82" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D82"/>
       <x:c r="E82"/>
       <x:c r="F82"/>
-      <x:c r="G82" t="str">
-        <x:v>弹丸投递阵型</x:v>
-      </x:c>
-      <x:c r="H82" t="str">
-        <x:v>Targeted</x:v>
-      </x:c>
+      <x:c r="G82"/>
+      <x:c r="H82"/>
       <x:c r="I82"/>
-      <x:c r="J82" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K82" t="str">
-        <x:v>Targeted</x:v>
-      </x:c>
+      <x:c r="J82"/>
+      <x:c r="K82"/>
       <x:c r="L82"/>
     </x:row>
     <x:row r="83">
       <x:c r="A83"/>
-      <x:c r="B83"/>
+      <x:c r="B83" t="str">
+        <x:v>EProjectilePattern</x:v>
+      </x:c>
       <x:c r="C83"/>
-      <x:c r="D83"/>
+      <x:c r="D83" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E83"/>
       <x:c r="F83"/>
-      <x:c r="G83"/>
+      <x:c r="G83" t="str">
+        <x:v>弹丸投递阵型</x:v>
+      </x:c>
       <x:c r="H83" t="str">
-        <x:v>Fan</x:v>
+        <x:v>Targeted</x:v>
       </x:c>
       <x:c r="I83"/>
       <x:c r="J83" t="n">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K83" t="str">
-        <x:v>Fan</x:v>
+        <x:v>Targeted</x:v>
       </x:c>
       <x:c r="L83"/>
     </x:row>
@@ -2782,93 +2791,128 @@
       <x:c r="F84"/>
       <x:c r="G84"/>
       <x:c r="H84" t="str">
-        <x:v>Radial</x:v>
+        <x:v>Fan</x:v>
       </x:c>
       <x:c r="I84"/>
       <x:c r="J84" t="n">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K84" t="str">
-        <x:v>Radial</x:v>
+        <x:v>Fan</x:v>
       </x:c>
       <x:c r="L84"/>
     </x:row>
     <x:row r="85">
       <x:c r="A85"/>
-      <x:c r="B85" t="str">
-        <x:v>ERunEventKind</x:v>
-      </x:c>
+      <x:c r="B85"/>
       <x:c r="C85"/>
-      <x:c r="D85" s="1" t="b">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="D85"/>
       <x:c r="E85"/>
       <x:c r="F85"/>
-      <x:c r="G85" t="str">
-        <x:v>关卡时间事件</x:v>
-      </x:c>
+      <x:c r="G85"/>
       <x:c r="H85" t="str">
-        <x:v>EliteSpawn</x:v>
+        <x:v>Radial</x:v>
       </x:c>
       <x:c r="I85"/>
       <x:c r="J85" t="n">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="K85" t="str">
-        <x:v>独立精英出现</x:v>
+        <x:v>Radial</x:v>
       </x:c>
       <x:c r="L85"/>
     </x:row>
     <x:row r="86">
       <x:c r="A86"/>
-      <x:c r="B86"/>
+      <x:c r="B86" t="str">
+        <x:v>ERunEventKind</x:v>
+      </x:c>
       <x:c r="C86"/>
-      <x:c r="D86"/>
+      <x:c r="D86" s="1" t="b">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E86"/>
       <x:c r="F86"/>
-      <x:c r="G86"/>
+      <x:c r="G86" t="str">
+        <x:v>关卡时间事件</x:v>
+      </x:c>
       <x:c r="H86" t="str">
-        <x:v>MapChest</x:v>
+        <x:v>EliteSpawn</x:v>
       </x:c>
       <x:c r="I86"/>
       <x:c r="J86" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K86" t="str">
+        <x:v>独立精英出现</x:v>
+      </x:c>
+      <x:c r="L86"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
+      <x:c r="H87" t="str">
+        <x:v>MapChest</x:v>
+      </x:c>
+      <x:c r="I87"/>
+      <x:c r="J87" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K86" t="str">
+      <x:c r="K87" t="str">
         <x:v>地图宝箱出现</x:v>
       </x:c>
-      <x:c r="L86"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="B87" t="str">
+      <x:c r="L87"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88"/>
+      <x:c r="B88" t="str">
         <x:v>ETribulationSignature</x:v>
       </x:c>
-      <x:c r="D87" s="1" t="b">
+      <x:c r="C88"/>
+      <x:c r="D88" s="1" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G87" t="str">
+      <x:c r="E88"/>
+      <x:c r="F88"/>
+      <x:c r="G88" t="str">
         <x:v>切片职业机制</x:v>
       </x:c>
-      <x:c r="H87" t="str">
+      <x:c r="H88" t="str">
         <x:v>Guard</x:v>
       </x:c>
-      <x:c r="J87" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K87" t="str">
+      <x:c r="I88"/>
+      <x:c r="J88" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K88" t="str">
         <x:v>有效受击蓄能铁壁</x:v>
       </x:c>
-    </x:row>
-    <x:row r="88">
-      <x:c r="H88" t="str">
+      <x:c r="L88"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89"/>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
+      <x:c r="H89" t="str">
         <x:v>Domains</x:v>
       </x:c>
-      <x:c r="J88" t="n">
+      <x:c r="I89"/>
+      <x:c r="J89" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="K88" t="str">
+      <x:c r="K89" t="str">
         <x:v>移动留阵重叠引爆</x:v>
       </x:c>
+      <x:c r="L89"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
